--- a/sitemap/glavis-sitemap-url-list.xlsx
+++ b/sitemap/glavis-sitemap-url-list.xlsx
@@ -13,10 +13,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="③グローバルナビ案" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="④ご確認事項" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑤ラフ案からの変更点" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑥監修者とGAページ対応" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'①GAサイト'!$A$3:$H$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'②HDサイト'!$A$3:$H$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'②HDサイト'!$A$3:$H$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'⑥監修者とGAページ対応'!$A$3:$F$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -194,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -322,6 +324,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -688,7 +699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B25"/>
+  <dimension ref="B2:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -760,7 +771,7 @@
     <row r="12">
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>②HDサイト　　　　記事をGAへ移した後のGLAVISグループのキュレーション構成（14行）</t>
+          <t>②HDサイト　　　　記事をGAへ移した後のGLAVISグループのキュレーション構成（15行）</t>
         </is>
       </c>
     </row>
@@ -774,7 +785,7 @@
     <row r="14">
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>④ご確認事項　　　ご判断をお願いしたい論点（9件）</t>
+          <t>④ご確認事項　　　ご判断をお願いしたい論点（11件）</t>
         </is>
       </c>
     </row>
@@ -786,62 +797,69 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="3" t="n"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>⑥監修者とGAページ対応　HD監修者17名とGAコンサルタントページの対応状況</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>色の見方</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>・薄い黄色の行　… 状態が「要確認」。ご判断が必要な箇所です（全12件）</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>・薄い灰色の行　… 状態が「次フェーズ」。今回の範囲外（10月以降・別予算）です</t>
+          <t>・薄い黄色の行　… 状態が「要確認」。ご判断が必要な箇所です（全13件）</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="5" t="inlineStr">
         <is>
+          <t>・薄い灰色の行　… 状態が「次フェーズ」。今回の範囲外（10月以降・別予算）です</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
           <t>・薄い水色の行　… 各サイトのトップページ</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="3" t="n"/>
-    </row>
     <row r="22">
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>ご確認方法</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>「補足・論点」列に★が付いている行が、特にご確認いただきたい箇所です。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>ご意見は本ファイルに直接ご記入いただくか、MTG②で口頭でも結構です。</t>
+          <t>「補足・論点」列に★が付いている行が、特にご確認いただきたい箇所です。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>ご意見は本ファイルに直接ご記入いただくか、MTG②で口頭でも結構です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>宛先：tsutomu.kado@mocamoco.com（加堂）／ kodama@itline.co.jp（小玉）</t>
         </is>
@@ -2413,7 +2431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2692,12 +2710,12 @@
       </c>
       <c r="B9" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">　監修者</t>
+          <t xml:space="preserve">　監修者・執筆者一覧</t>
         </is>
       </c>
       <c r="C9" s="25" t="inlineStr">
         <is>
-          <t>（URL未確認）</t>
+          <t>https://www.glavis-hd.com/author/</t>
         </is>
       </c>
       <c r="D9" s="40" t="inlineStr">
@@ -2712,137 +2730,141 @@
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
+          <t>不要</t>
+        </is>
+      </c>
+      <c r="G9" s="24" t="inlineStr">
+        <is>
+          <t>HDに残置。URL変更なし</t>
+        </is>
+      </c>
+      <c r="H9" s="24" t="inlineStr">
+        <is>
+          <t>★8/10 方針変更で残置。17名分が1ページに並ぶ構成で、個人ページはありません。各記事からは /author/?author={ID} のクエリ付きURLで該当箇所へ遷移します</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>第2階層</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　監修者 個別（アンカー）</t>
+        </is>
+      </c>
+      <c r="C10" s="25" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/author/?author={ID}</t>
+        </is>
+      </c>
+      <c r="D10" s="40" t="inlineStr">
+        <is>
+          <t>HDサイトから</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="G9" s="24" t="inlineStr">
-        <is>
-          <t>現行URLが未把握のため判定できません</t>
-        </is>
-      </c>
-      <c r="H9" s="24" t="inlineStr">
-        <is>
-          <t>★8/10 方針変更で残置。ただし現行URL一覧173件に監修者ページが含まれておらず、URL・ページ数が未把握です。ご共有をお願いします</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>不要</t>
+        </is>
+      </c>
+      <c r="G10" s="24" t="inlineStr">
+        <is>
+          <t>HDに残置。URL変更なし</t>
+        </is>
+      </c>
+      <c r="H10" s="24" t="inlineStr">
+        <is>
+          <t>実体は上記1ページ内のアンカー（#author-{ID}）。全記事の「この記事の監修者」リンク先</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>第1階層</t>
         </is>
       </c>
-      <c r="B10" s="27" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">　お問い合わせ・お申し込み</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>https://www.glavis-hd.com/inquiry/</t>
         </is>
       </c>
-      <c r="D10" s="32" t="inlineStr">
+      <c r="D11" s="30" t="inlineStr">
         <is>
           <t>HDサイトから</t>
         </is>
       </c>
-      <c r="E10" s="19" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>確定</t>
         </is>
       </c>
-      <c r="F10" s="19" t="inlineStr">
+      <c r="F11" s="14" t="inlineStr">
         <is>
           <t>不要</t>
         </is>
       </c>
-      <c r="G10" s="20" t="inlineStr">
+      <c r="G11" s="18" t="inlineStr">
         <is>
           <t>HDに残置。URL変更なし</t>
         </is>
       </c>
-      <c r="H10" s="20" t="inlineStr"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="23" t="inlineStr">
+      <c r="H11" s="18" t="inlineStr"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="23" t="inlineStr">
         <is>
           <t>第1階層</t>
         </is>
       </c>
-      <c r="B11" s="28" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">　採用お問い合わせ・エントリー</t>
         </is>
       </c>
-      <c r="C11" s="25" t="inlineStr">
+      <c r="C12" s="25" t="inlineStr">
         <is>
           <t>https://www.glavis-hd.com/inquiry_recruit/</t>
         </is>
       </c>
-      <c r="D11" s="40" t="inlineStr">
+      <c r="D12" s="40" t="inlineStr">
         <is>
           <t>HDサイトから</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="F11" s="23" t="inlineStr">
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t>不要</t>
         </is>
       </c>
-      <c r="G11" s="24" t="inlineStr">
+      <c r="G12" s="24" t="inlineStr">
         <is>
           <t>HDに残置。URL変更なし</t>
         </is>
       </c>
-      <c r="H11" s="24" t="inlineStr">
+      <c r="H12" s="24" t="inlineStr">
         <is>
           <t>採用サイトのGA移設にともない、HD側に残すか要確認</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>第1階層</t>
-        </is>
-      </c>
-      <c r="B12" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　プライバシーポリシー</t>
-        </is>
-      </c>
-      <c r="C12" s="21" t="inlineStr">
-        <is>
-          <t>https://www.glavis-hd.com/privacy_policy/</t>
-        </is>
-      </c>
-      <c r="D12" s="32" t="inlineStr">
-        <is>
-          <t>HDサイトから</t>
-        </is>
-      </c>
-      <c r="E12" s="19" t="inlineStr">
-        <is>
-          <t>確定</t>
-        </is>
-      </c>
-      <c r="F12" s="19" t="inlineStr">
-        <is>
-          <t>不要</t>
-        </is>
-      </c>
-      <c r="G12" s="20" t="inlineStr">
-        <is>
-          <t>HDに残置。URL変更なし</t>
-        </is>
-      </c>
-      <c r="H12" s="20" t="inlineStr"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="14" t="inlineStr">
@@ -2852,12 +2874,12 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">　サイトポリシー</t>
+          <t xml:space="preserve">　プライバシーポリシー</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
-          <t>https://www.glavis-hd.com/site_policy/</t>
+          <t>https://www.glavis-hd.com/privacy_policy/</t>
         </is>
       </c>
       <c r="D13" s="30" t="inlineStr">
@@ -2890,77 +2912,73 @@
       </c>
       <c r="B14" s="27" t="inlineStr">
         <is>
+          <t xml:space="preserve">　サイトポリシー</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/site_policy/</t>
+        </is>
+      </c>
+      <c r="D14" s="32" t="inlineStr">
+        <is>
+          <t>HDサイトから</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="F14" s="19" t="inlineStr">
+        <is>
+          <t>不要</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>HDに残置。URL変更なし</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>第1階層</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
           <t xml:space="preserve">　ソーシャルメディアポリシー</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>https://www.glavis-hd.com/sns_policy/</t>
         </is>
       </c>
-      <c r="D14" s="32" t="inlineStr">
+      <c r="D15" s="30" t="inlineStr">
         <is>
           <t>HDサイトから</t>
         </is>
       </c>
-      <c r="E14" s="19" t="inlineStr">
+      <c r="E15" s="14" t="inlineStr">
         <is>
           <t>確定</t>
         </is>
       </c>
-      <c r="F14" s="19" t="inlineStr">
+      <c r="F15" s="14" t="inlineStr">
         <is>
           <t>不要</t>
         </is>
       </c>
-      <c r="G14" s="20" t="inlineStr">
+      <c r="G15" s="18" t="inlineStr">
         <is>
           <t>HDに残置。URL変更なし</t>
         </is>
       </c>
-      <c r="H14" s="20" t="inlineStr"/>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="23" t="inlineStr">
-        <is>
-          <t>第1階層</t>
-        </is>
-      </c>
-      <c r="B15" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　社会問題への解決アプローチ</t>
-        </is>
-      </c>
-      <c r="C15" s="25" t="inlineStr">
-        <is>
-          <t>https://www.glavis-hd.com/case/</t>
-        </is>
-      </c>
-      <c r="D15" s="40" t="inlineStr">
-        <is>
-          <t>HDサイトから</t>
-        </is>
-      </c>
-      <c r="E15" s="23" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F15" s="23" t="inlineStr">
-        <is>
-          <t>不要</t>
-        </is>
-      </c>
-      <c r="G15" s="24" t="inlineStr">
-        <is>
-          <t>HDに残置。URL変更なし</t>
-        </is>
-      </c>
-      <c r="H15" s="24" t="inlineStr">
-        <is>
-          <t>★47記事はGAへ移行。一覧ページ自体を残すか、GAへ転送するか要確認</t>
-        </is>
-      </c>
+      <c r="H15" s="18" t="inlineStr"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="23" t="inlineStr">
@@ -2970,12 +2988,12 @@
       </c>
       <c r="B16" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">　日本の社会問題</t>
+          <t xml:space="preserve">　社会問題への解決アプローチ</t>
         </is>
       </c>
       <c r="C16" s="25" t="inlineStr">
         <is>
-          <t>https://www.glavis-hd.com/social_problem/</t>
+          <t>https://www.glavis-hd.com/case/</t>
         </is>
       </c>
       <c r="D16" s="40" t="inlineStr">
@@ -3000,54 +3018,96 @@
       </c>
       <c r="H16" s="24" t="inlineStr">
         <is>
-          <t>★25記事はGAへ移行。インフォグラフィックDL導線の扱いを要確認</t>
+          <t>★47記事はGAへ移行。一覧ページ自体を残すか、GAへ転送するか要確認</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="23" t="inlineStr">
         <is>
+          <t>第1階層</t>
+        </is>
+      </c>
+      <c r="B17" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　日本の社会問題</t>
+        </is>
+      </c>
+      <c r="C17" s="25" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/social_problem/</t>
+        </is>
+      </c>
+      <c r="D17" s="40" t="inlineStr">
+        <is>
+          <t>HDサイトから</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>不要</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="inlineStr">
+        <is>
+          <t>HDに残置。URL変更なし</t>
+        </is>
+      </c>
+      <c r="H17" s="24" t="inlineStr">
+        <is>
+          <t>★25記事はGAへ移行。インフォグラフィックDL導線の扱いを要確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="23" t="inlineStr">
+        <is>
           <t>第2階層</t>
         </is>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B18" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">　　インフォグラフィック一覧</t>
         </is>
       </c>
-      <c r="C17" s="25" t="inlineStr">
+      <c r="C18" s="25" t="inlineStr">
         <is>
           <t>https://www.glavis-hd.com/social_problem/download/</t>
         </is>
       </c>
-      <c r="D17" s="40" t="inlineStr">
+      <c r="D18" s="40" t="inlineStr">
         <is>
           <t>HDサイトから</t>
         </is>
       </c>
-      <c r="E17" s="23" t="inlineStr">
+      <c r="E18" s="23" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="F17" s="23" t="inlineStr">
+      <c r="F18" s="23" t="inlineStr">
         <is>
           <t>不要</t>
         </is>
       </c>
-      <c r="G17" s="24" t="inlineStr">
+      <c r="G18" s="24" t="inlineStr">
         <is>
           <t>HDに残置。URL変更なし</t>
         </is>
       </c>
-      <c r="H17" s="24" t="inlineStr">
+      <c r="H18" s="24" t="inlineStr">
         <is>
           <t>DL申込フォーム・完了ページを含む4ページ。掲載先が決まり次第リダイレクト設定</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H17"/>
+  <autoFilter ref="A3:H18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3358,7 +3418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3562,17 +3622,17 @@
       </c>
       <c r="B11" s="18" t="inlineStr">
         <is>
-          <t>HD「監修者」ページのURL</t>
+          <t>GA記事からの監修者リンクの向き先</t>
         </is>
       </c>
       <c r="C11" s="18" t="inlineStr">
         <is>
-          <t>★残置が決まりましたが、ご提供いただいた現行URL一覧173件に監修者ページが含まれておらず、URL・ページ数を把握できていません。ご共有をお願いします。</t>
+          <t>★現在、全記事の「この記事の監修者」は HD の /author/?author={ID} を指しています。記事がGAへ移った後もHDへ戻す動線のままでよいか、GAの「コンサルタント」ページへ向けるかをご判断ください。</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>9/5</t>
+          <t>8/31</t>
         </is>
       </c>
       <c r="E11" s="45" t="n"/>
@@ -3583,20 +3643,62 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
+          <t>監修者17名とGAコンサルタントページの対応</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>★監修者17名のうち、GAに個人ページがあるのは7名のみです。8名はGAトップへのリンクのみ、2名は他社（PTM・AmbiRise）でした。GA側へ動線を寄せる場合、8名分のページ作成要否のご判断が必要です。</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>9/5</t>
+        </is>
+      </c>
+      <c r="E12" s="45" t="n"/>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>クエリ文字列付きURLのリダイレクト</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>監修者リンクは /author/?author=38 のようにクエリ文字列で個人を指定しています。転送先を変える場合はクエリ単位の設定が必要になるため、方針決定後にITLINEで対応します。</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>9/20</t>
+        </is>
+      </c>
+      <c r="E13" s="45" t="n"/>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="19" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
           <t>GA「会社概要」「お問い合わせ」</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>ラフ案に記載がありますがGA現行に単独ページが存在しません。新設するか、現在の導線のままとするかをご確認ください。</t>
         </is>
       </c>
-      <c r="D12" s="19" t="inlineStr">
+      <c r="D14" s="19" t="inlineStr">
         <is>
           <t>8/31</t>
         </is>
       </c>
-      <c r="E12" s="45" t="n"/>
+      <c r="E14" s="45" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3767,4 +3869,590 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>HD「監修者・執筆者一覧」17名とGAコンサルタントページの対応</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>2026年8月10日時点の https://www.glavis-hd.com/author/ の掲載内容より作成。GA個人ページがあるのは7名のみです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>author ID</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>氏名</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>所属・役職</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>現在の遷移先</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>GA個人ページの有無</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C4" s="46" t="inlineStr">
+        <is>
+          <t>古見 彰里</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>グラビス・アーキテクツ 代表</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com/（トップ）</t>
+        </is>
+      </c>
+      <c r="F4" s="23" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="C5" s="46" t="inlineStr">
+        <is>
+          <t>光延 裕司</t>
+        </is>
+      </c>
+      <c r="D5" s="24" t="inlineStr">
+        <is>
+          <t>グラビス・アーキテクツ 専務取締役</t>
+        </is>
+      </c>
+      <c r="E5" s="25" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com/（トップ）</t>
+        </is>
+      </c>
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="C6" s="47" t="inlineStr">
+        <is>
+          <t>川人 伸</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>グラビス・アーキテクツ パートナー／PTM 代表取締役</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>他社（PTM）</t>
+        </is>
+      </c>
+      <c r="F6" s="19" t="inlineStr">
+        <is>
+          <t>－（他社）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="C7" s="48" t="inlineStr">
+        <is>
+          <t>四田 耕三</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>グラビス・アーキテクツ パートナー</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com/member/000469/</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="C8" s="47" t="inlineStr">
+        <is>
+          <t>清水 元幾</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>グラビス・アーキテクツ パートナー</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com/member/000464/</t>
+        </is>
+      </c>
+      <c r="F8" s="19" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>542</t>
+        </is>
+      </c>
+      <c r="C9" s="48" t="inlineStr">
+        <is>
+          <t>大塚 洋一</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>グラビス・アーキテクツ プリンシパルアーキテクト</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com/member/000481/</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="C10" s="47" t="inlineStr">
+        <is>
+          <t>福田 次郎</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>グラビス・アーキテクツ プリンシパルアーキテクト</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com/member/000607/</t>
+        </is>
+      </c>
+      <c r="F10" s="19" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="C11" s="48" t="inlineStr">
+        <is>
+          <t>若山 英己</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>グラビス・アーキテクツ プリンシパルアーキテクト</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com/member/000605/</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="C12" s="47" t="inlineStr">
+        <is>
+          <t>葛西 哲郎</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>グラビス・アーキテクツ ディレクター</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com/member/000480/</t>
+        </is>
+      </c>
+      <c r="F12" s="19" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>660</t>
+        </is>
+      </c>
+      <c r="C13" s="46" t="inlineStr">
+        <is>
+          <t>井上 泰一</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>グラビス・アーキテクツ シニアマネージャ</t>
+        </is>
+      </c>
+      <c r="E13" s="25" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com/（トップ）</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>581</t>
+        </is>
+      </c>
+      <c r="C14" s="46" t="inlineStr">
+        <is>
+          <t>根崎 耕一</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>グラビス・アーキテクツ シニアマネージャ</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com/（トップ）</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="C15" s="48" t="inlineStr">
+        <is>
+          <t>山下 達哉</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>グラビス・アーキテクツ シニアマネージャ</t>
+        </is>
+      </c>
+      <c r="E15" s="16" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com/member/000482/</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="23" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="C16" s="46" t="inlineStr">
+        <is>
+          <t>内田 英之</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>グラビス・アーキテクツ マネージャ</t>
+        </is>
+      </c>
+      <c r="E16" s="25" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com/（トップ）</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="23" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>419</t>
+        </is>
+      </c>
+      <c r="C17" s="46" t="inlineStr">
+        <is>
+          <t>大塚 貴</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>グラビス・アーキテクツ マネージャ</t>
+        </is>
+      </c>
+      <c r="E17" s="25" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com/（トップ）</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="23" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="C18" s="46" t="inlineStr">
+        <is>
+          <t>木場 俊介</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>グラビス・アーキテクツ シニアコンサルタント</t>
+        </is>
+      </c>
+      <c r="E18" s="25" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com/（トップ）</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="23" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>411</t>
+        </is>
+      </c>
+      <c r="C19" s="46" t="inlineStr">
+        <is>
+          <t>鈴木 啓仁</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>グラビス・アーキテクツ シニアコンサルタント</t>
+        </is>
+      </c>
+      <c r="E19" s="25" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com/（トップ）</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="C20" s="47" t="inlineStr">
+        <is>
+          <t>田中 寛純</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>株式会社AmbiRise 業務アドバイザー</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>他社（AmbiRise）</t>
+        </is>
+      </c>
+      <c r="F20" s="19" t="inlineStr">
+        <is>
+          <t>－（他社）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>GA個人ページあり 7名／なし 8名／他社 2名</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:F20"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/sitemap/glavis-sitemap-url-list.xlsx
+++ b/sitemap/glavis-sitemap-url-list.xlsx
@@ -16,8 +16,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑥監修者とGAページ対応" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'①GAサイト'!$A$3:$H$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'②HDサイト'!$A$3:$H$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'①GAサイト'!$A$3:$H$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'②HDサイト'!$A$3:$H$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'⑥監修者とGAページ対応'!$A$3:$F$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -284,18 +284,18 @@
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -311,7 +311,7 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -764,14 +764,14 @@
     <row r="11">
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>①GAサイト　　　　新しいグラビス・アーキテクツのサイト構成（37行）</t>
+          <t>①GAサイト　　　　新しいグラビス・アーキテクツのサイト構成（38行）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>②HDサイト　　　　記事をGAへ移した後のGLAVISグループのキュレーション構成（15行）</t>
+          <t>②HDサイト　　　　記事をGAへ移した後のGLAVISグループのキュレーション構成（10行）</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
     <row r="14">
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>④ご確認事項　　　ご判断をお願いしたい論点（11件）</t>
+          <t>④ご確認事項　　　ご判断をお願いしたい論点（9件）</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
     <row r="19">
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>・薄い黄色の行　… 状態が「要確認」。ご判断が必要な箇所です（全13件）</t>
+          <t>・薄い黄色の行　… 状態が「要確認」。ご判断が必要な箇所です（全10件）</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1626,22 +1626,22 @@
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="23" t="inlineStr">
         <is>
-          <t>第1階層</t>
-        </is>
-      </c>
-      <c r="B21" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　お客様</t>
+          <t>第2階層</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　インフォグラフィック一覧</t>
         </is>
       </c>
       <c r="C21" s="25" t="inlineStr">
         <is>
-          <t>https://www.glavisarchitects.com/customer/</t>
-        </is>
-      </c>
-      <c r="D21" s="29" t="inlineStr">
-        <is>
-          <t>新規ページ</t>
+          <t>https://www.glavisarchitects.com/agenda/download/</t>
+        </is>
+      </c>
+      <c r="D21" s="31" t="inlineStr">
+        <is>
+          <t>HDサイトから</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
@@ -1651,119 +1651,119 @@
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
-          <t>不要</t>
+          <t>必要</t>
         </is>
       </c>
       <c r="G21" s="24" t="inlineStr">
         <is>
-          <t>新規ページのため旧URLなし</t>
+          <t>旧：https://www.glavis-hd.com の該当ページからの転送</t>
         </is>
       </c>
       <c r="H21" s="24" t="inlineStr">
         <is>
-          <t>★新設・準備中。記事の実体は今後グラビス様にてご用意。名称未定</t>
+          <t>★8/13 岡田様ご判断によりGAへ移行。HD /social_problem/download/ のDL申込フォーム・完了ページを含む4ページ。配置先URLは要確認</t>
         </is>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="23" t="inlineStr">
         <is>
+          <t>第1階層</t>
+        </is>
+      </c>
+      <c r="B22" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　お客様</t>
+        </is>
+      </c>
+      <c r="C22" s="25" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com/customer/</t>
+        </is>
+      </c>
+      <c r="D22" s="29" t="inlineStr">
+        <is>
+          <t>新規ページ</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F22" s="23" t="inlineStr">
+        <is>
+          <t>不要</t>
+        </is>
+      </c>
+      <c r="G22" s="24" t="inlineStr">
+        <is>
+          <t>新規ページのため旧URLなし</t>
+        </is>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
+        <is>
+          <t>★新設・準備中。記事の実体は今後グラビス様にてご用意。名称未定</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="23" t="inlineStr">
+        <is>
           <t>第2階層</t>
         </is>
       </c>
-      <c r="B22" s="24" t="inlineStr">
+      <c r="B23" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">　　お客様（記事）</t>
         </is>
       </c>
-      <c r="C22" s="25" t="inlineStr">
+      <c r="C23" s="25" t="inlineStr">
         <is>
           <t>https://www.glavisarchitects.com/customer/{id}/</t>
         </is>
       </c>
-      <c r="D22" s="29" t="inlineStr">
+      <c r="D23" s="29" t="inlineStr">
         <is>
           <t>新規ページ</t>
         </is>
       </c>
-      <c r="E22" s="23" t="inlineStr">
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="F22" s="23" t="inlineStr">
+      <c r="F23" s="23" t="inlineStr">
         <is>
           <t>不要</t>
         </is>
       </c>
-      <c r="G22" s="24" t="inlineStr">
+      <c r="G23" s="24" t="inlineStr">
         <is>
           <t>新規ページのため旧URLなし</t>
         </is>
       </c>
-      <c r="H22" s="24" t="inlineStr"/>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="14" t="inlineStr">
-        <is>
-          <t>第1階層</t>
-        </is>
-      </c>
-      <c r="B23" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　有識者インタビュー</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>https://www.glavisarchitects.com/interview/</t>
-        </is>
-      </c>
-      <c r="D23" s="31" t="inlineStr">
-        <is>
-          <t>新規ページ</t>
-        </is>
-      </c>
-      <c r="E23" s="14" t="inlineStr">
-        <is>
-          <t>確定</t>
-        </is>
-      </c>
-      <c r="F23" s="14" t="inlineStr">
-        <is>
-          <t>不要</t>
-        </is>
-      </c>
-      <c r="G23" s="18" t="inlineStr">
-        <is>
-          <t>新規ページのため旧URLなし</t>
-        </is>
-      </c>
-      <c r="H23" s="18" t="inlineStr">
-        <is>
-          <t>★新設。HD「解決アプローチ＞対談」の記事を移行</t>
-        </is>
-      </c>
+      <c r="H23" s="24" t="inlineStr"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="19" t="inlineStr">
         <is>
-          <t>第2階層</t>
-        </is>
-      </c>
-      <c r="B24" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　有識者インタビュー（記事）</t>
+          <t>第1階層</t>
+        </is>
+      </c>
+      <c r="B24" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　有識者インタビュー</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
         <is>
-          <t>https://www.glavisarchitects.com/interview/{id}/</t>
+          <t>https://www.glavisarchitects.com/interview/</t>
         </is>
       </c>
       <c r="D24" s="32" t="inlineStr">
         <is>
-          <t>HDサイトから</t>
+          <t>新規ページ</t>
         </is>
       </c>
       <c r="E24" s="19" t="inlineStr">
@@ -1773,35 +1773,39 @@
       </c>
       <c r="F24" s="19" t="inlineStr">
         <is>
-          <t>必要</t>
+          <t>不要</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
         <is>
-          <t>旧：https://www.glavis-hd.com の該当ページからの転送</t>
-        </is>
-      </c>
-      <c r="H24" s="20" t="inlineStr"/>
+          <t>新規ページのため旧URLなし</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>★新設。HD「解決アプローチ＞対談」の記事を移行</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>第1階層</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　コンサルタント</t>
+          <t>第2階層</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　有識者インタビュー（記事）</t>
         </is>
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>https://www.glavisarchitects.com/member/</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>GAサイトから</t>
+          <t>https://www.glavisarchitects.com/interview/{id}/</t>
+        </is>
+      </c>
+      <c r="D25" s="30" t="inlineStr">
+        <is>
+          <t>HDサイトから</t>
         </is>
       </c>
       <c r="E25" s="14" t="inlineStr">
@@ -1811,34 +1815,30 @@
       </c>
       <c r="F25" s="14" t="inlineStr">
         <is>
-          <t>不要</t>
+          <t>必要</t>
         </is>
       </c>
       <c r="G25" s="18" t="inlineStr">
         <is>
-          <t>GA既存。URL変更なし</t>
-        </is>
-      </c>
-      <c r="H25" s="18" t="inlineStr">
-        <is>
-          <t>★方針変更。HD「監修者」ページとの統合はせず、監修者ページはHDに残置（8/10）</t>
-        </is>
-      </c>
+          <t>旧：https://www.glavis-hd.com の該当ページからの転送</t>
+        </is>
+      </c>
+      <c r="H25" s="18" t="inlineStr"/>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="19" t="inlineStr">
         <is>
-          <t>第2階層</t>
-        </is>
-      </c>
-      <c r="B26" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　コンサルタント（個人ページ）</t>
+          <t>第1階層</t>
+        </is>
+      </c>
+      <c r="B26" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　コンサルタント</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>https://www.glavisarchitects.com/member/{id}/</t>
+          <t>https://www.glavisarchitects.com/member/</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -1863,111 +1863,111 @@
       </c>
       <c r="H26" s="20" t="inlineStr">
         <is>
-          <t>GAに記事を掲載するコンサルメンバーは必ず紹介を掲載</t>
+          <t>★8/13 岡田様ご判断により、HD「監修者・執筆者一覧」をGAへ移しコンサルタントへ統合する（8/10 大島様の「HDに残す」から再変更）</t>
         </is>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="23" t="inlineStr">
         <is>
+          <t>第2階層</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　コンサルタント（個人ページ）</t>
+        </is>
+      </c>
+      <c r="C27" s="25" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com/member/{id}/</t>
+        </is>
+      </c>
+      <c r="D27" s="26" t="inlineStr">
+        <is>
+          <t>GAサイトから</t>
+        </is>
+      </c>
+      <c r="E27" s="23" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="inlineStr">
+        <is>
+          <t>配置が変わる場合は転送が必要</t>
+        </is>
+      </c>
+      <c r="H27" s="24" t="inlineStr">
+        <is>
+          <t>★監修者17名と同じ立ち位置に揃える。GA個人ページがあるのは7名のみで、8名は未作成・2名は他社（PTM／AmbiRise）。未作成8名の扱いは要ご判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="23" t="inlineStr">
+        <is>
           <t>第1階層</t>
         </is>
       </c>
-      <c r="B27" s="28" t="inlineStr">
+      <c r="B28" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">　ニュース</t>
         </is>
       </c>
-      <c r="C27" s="25" t="inlineStr">
+      <c r="C28" s="25" t="inlineStr">
         <is>
           <t>https://www.glavisarchitects.com/news/</t>
         </is>
       </c>
-      <c r="D27" s="29" t="inlineStr">
+      <c r="D28" s="29" t="inlineStr">
         <is>
           <t>新規ページ</t>
         </is>
       </c>
-      <c r="E27" s="23" t="inlineStr">
+      <c r="E28" s="23" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="F27" s="23" t="inlineStr">
+      <c r="F28" s="23" t="inlineStr">
         <is>
           <t>不要</t>
         </is>
       </c>
-      <c r="G27" s="24" t="inlineStr">
+      <c r="G28" s="24" t="inlineStr">
         <is>
           <t>新規ページのため旧URLなし</t>
         </is>
       </c>
-      <c r="H27" s="24" t="inlineStr">
+      <c r="H28" s="24" t="inlineStr">
         <is>
           <t>★GA現行にニュースページは存在しません（ラフ案では「GAサイトから」となっていますが要確認）。HDのニュース85件はHDに残る前提のため、GA側に新設するかどうかのご判断が必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>第1階層</t>
-        </is>
-      </c>
-      <c r="B28" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　採用情報</t>
-        </is>
-      </c>
-      <c r="C28" s="21" t="inlineStr">
-        <is>
-          <t>https://www.glavisarchitects.com/recruit/</t>
-        </is>
-      </c>
-      <c r="D28" s="33" t="inlineStr">
-        <is>
-          <t>採用サイトから</t>
-        </is>
-      </c>
-      <c r="E28" s="19" t="inlineStr">
-        <is>
-          <t>確定</t>
-        </is>
-      </c>
-      <c r="F28" s="19" t="inlineStr">
-        <is>
-          <t>必要</t>
-        </is>
-      </c>
-      <c r="G28" s="20" t="inlineStr">
-        <is>
-          <t>旧：https://www.glavis-hd.com/recruit/ga/… からの転送</t>
-        </is>
-      </c>
-      <c r="H28" s="20" t="inlineStr">
-        <is>
-          <t>HD配下からGA配下へ移設。301リダイレクト対象60ページ</t>
         </is>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="14" t="inlineStr">
         <is>
-          <t>第2階層</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　キャリア採用求人一覧</t>
+          <t>第1階層</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　採用情報</t>
         </is>
       </c>
       <c r="C29" s="16" t="inlineStr">
         <is>
-          <t>https://www.glavisarchitects.com/recruit/career_menu/</t>
-        </is>
-      </c>
-      <c r="D29" s="34" t="inlineStr">
+          <t>https://www.glavisarchitects.com/recruit/</t>
+        </is>
+      </c>
+      <c r="D29" s="33" t="inlineStr">
         <is>
           <t>採用サイトから</t>
         </is>
@@ -1987,7 +1987,11 @@
           <t>旧：https://www.glavis-hd.com/recruit/ga/… からの転送</t>
         </is>
       </c>
-      <c r="H29" s="18" t="inlineStr"/>
+      <c r="H29" s="18" t="inlineStr">
+        <is>
+          <t>HD配下からGA配下へ移設。301リダイレクト対象60ページ</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="19" t="inlineStr">
@@ -1997,15 +2001,15 @@
       </c>
       <c r="B30" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　キャリア設計</t>
+          <t xml:space="preserve">　　キャリア採用求人一覧</t>
         </is>
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>https://www.glavisarchitects.com/recruit/careerplan/</t>
-        </is>
-      </c>
-      <c r="D30" s="33" t="inlineStr">
+          <t>https://www.glavisarchitects.com/recruit/career_menu/</t>
+        </is>
+      </c>
+      <c r="D30" s="34" t="inlineStr">
         <is>
           <t>採用サイトから</t>
         </is>
@@ -2035,15 +2039,15 @@
       </c>
       <c r="B31" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　はたらく環境</t>
+          <t xml:space="preserve">　　キャリア設計</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
         <is>
-          <t>https://www.glavisarchitects.com/recruit/environment/</t>
-        </is>
-      </c>
-      <c r="D31" s="34" t="inlineStr">
+          <t>https://www.glavisarchitects.com/recruit/careerplan/</t>
+        </is>
+      </c>
+      <c r="D31" s="33" t="inlineStr">
         <is>
           <t>採用サイトから</t>
         </is>
@@ -2073,15 +2077,15 @@
       </c>
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　はたらき方</t>
+          <t xml:space="preserve">　　はたらく環境</t>
         </is>
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>https://www.glavisarchitects.com/recruit/workstyle/</t>
-        </is>
-      </c>
-      <c r="D32" s="33" t="inlineStr">
+          <t>https://www.glavisarchitects.com/recruit/environment/</t>
+        </is>
+      </c>
+      <c r="D32" s="34" t="inlineStr">
         <is>
           <t>採用サイトから</t>
         </is>
@@ -2111,15 +2115,15 @@
       </c>
       <c r="B33" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　社員紹介</t>
+          <t xml:space="preserve">　　はたらき方</t>
         </is>
       </c>
       <c r="C33" s="16" t="inlineStr">
         <is>
-          <t>https://www.glavisarchitects.com/recruit/member/</t>
-        </is>
-      </c>
-      <c r="D33" s="34" t="inlineStr">
+          <t>https://www.glavisarchitects.com/recruit/workstyle/</t>
+        </is>
+      </c>
+      <c r="D33" s="33" t="inlineStr">
         <is>
           <t>採用サイトから</t>
         </is>
@@ -2149,199 +2153,199 @@
       </c>
       <c r="B34" s="20" t="inlineStr">
         <is>
+          <t xml:space="preserve">　　社員紹介</t>
+        </is>
+      </c>
+      <c r="C34" s="21" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com/recruit/member/</t>
+        </is>
+      </c>
+      <c r="D34" s="34" t="inlineStr">
+        <is>
+          <t>採用サイトから</t>
+        </is>
+      </c>
+      <c r="E34" s="19" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="F34" s="19" t="inlineStr">
+        <is>
+          <t>必要</t>
+        </is>
+      </c>
+      <c r="G34" s="20" t="inlineStr">
+        <is>
+          <t>旧：https://www.glavis-hd.com/recruit/ga/… からの転送</t>
+        </is>
+      </c>
+      <c r="H34" s="20" t="inlineStr"/>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>第2階層</t>
+        </is>
+      </c>
+      <c r="B35" s="18" t="inlineStr">
+        <is>
           <t xml:space="preserve">　　よくいただくご質問</t>
         </is>
       </c>
-      <c r="C34" s="21" t="inlineStr">
+      <c r="C35" s="16" t="inlineStr">
         <is>
           <t>https://www.glavisarchitects.com/recruit/faq/</t>
         </is>
       </c>
-      <c r="D34" s="33" t="inlineStr">
+      <c r="D35" s="33" t="inlineStr">
         <is>
           <t>採用サイトから</t>
         </is>
       </c>
-      <c r="E34" s="19" t="inlineStr">
+      <c r="E35" s="14" t="inlineStr">
         <is>
           <t>確定</t>
         </is>
       </c>
-      <c r="F34" s="19" t="inlineStr">
+      <c r="F35" s="14" t="inlineStr">
         <is>
           <t>必要</t>
         </is>
       </c>
-      <c r="G34" s="20" t="inlineStr">
+      <c r="G35" s="18" t="inlineStr">
         <is>
           <t>旧：https://www.glavis-hd.com/recruit/ga/… からの転送</t>
         </is>
       </c>
-      <c r="H34" s="20" t="inlineStr"/>
-    </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="35" t="inlineStr">
+      <c r="H35" s="18" t="inlineStr"/>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="35" t="inlineStr">
         <is>
           <t>第2階層</t>
         </is>
       </c>
-      <c r="B35" s="36" t="inlineStr">
+      <c r="B36" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">　　事業内容（採用）</t>
         </is>
       </c>
-      <c r="C35" s="37" t="inlineStr">
+      <c r="C36" s="37" t="inlineStr">
         <is>
           <t>https://www.glavisarchitects.com/recruit/ourwork/</t>
         </is>
       </c>
-      <c r="D35" s="38" t="inlineStr">
+      <c r="D36" s="38" t="inlineStr">
         <is>
           <t>採用サイトから</t>
         </is>
       </c>
-      <c r="E35" s="35" t="inlineStr">
+      <c r="E36" s="35" t="inlineStr">
         <is>
           <t>次フェーズ</t>
         </is>
       </c>
-      <c r="F35" s="35" t="inlineStr">
+      <c r="F36" s="35" t="inlineStr">
         <is>
           <t>必要</t>
         </is>
       </c>
-      <c r="G35" s="36" t="inlineStr">
+      <c r="G36" s="36" t="inlineStr">
         <is>
           <t>旧：https://www.glavis-hd.com/recruit/ga/… からの転送</t>
         </is>
       </c>
-      <c r="H35" s="36" t="inlineStr">
+      <c r="H36" s="36" t="inlineStr">
         <is>
           <t>★GA「事業内容」との統合は次フェーズ・別予算。今回はそのまま移設</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="19" t="inlineStr">
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="14" t="inlineStr">
         <is>
           <t>第2階層</t>
         </is>
       </c>
-      <c r="B36" s="20" t="inlineStr">
+      <c r="B37" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">　　採用お問い合わせ</t>
         </is>
       </c>
-      <c r="C36" s="21" t="inlineStr">
+      <c r="C37" s="16" t="inlineStr">
         <is>
           <t>https://www.glavisarchitects.com/recruit/inquiry/</t>
         </is>
       </c>
-      <c r="D36" s="33" t="inlineStr">
+      <c r="D37" s="33" t="inlineStr">
         <is>
           <t>採用サイトから</t>
         </is>
       </c>
-      <c r="E36" s="19" t="inlineStr">
+      <c r="E37" s="14" t="inlineStr">
         <is>
           <t>確定</t>
         </is>
       </c>
-      <c r="F36" s="19" t="inlineStr">
+      <c r="F37" s="14" t="inlineStr">
         <is>
           <t>必要</t>
         </is>
       </c>
-      <c r="G36" s="20" t="inlineStr">
+      <c r="G37" s="18" t="inlineStr">
         <is>
           <t>旧：https://www.glavis-hd.com/recruit/ga/… からの転送</t>
         </is>
       </c>
-      <c r="H36" s="20" t="inlineStr">
+      <c r="H37" s="18" t="inlineStr">
         <is>
           <t>HD側フォームからの移設</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="23" t="inlineStr">
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="23" t="inlineStr">
         <is>
           <t>第1階層</t>
         </is>
       </c>
-      <c r="B37" s="28" t="inlineStr">
+      <c r="B38" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">　お問い合わせ</t>
         </is>
       </c>
-      <c r="C37" s="25" t="inlineStr">
+      <c r="C38" s="25" t="inlineStr">
         <is>
           <t>https://www.glavisarchitects.com/inquiry/</t>
         </is>
       </c>
-      <c r="D37" s="26" t="inlineStr">
+      <c r="D38" s="26" t="inlineStr">
         <is>
           <t>GAサイトから</t>
         </is>
       </c>
-      <c r="E37" s="23" t="inlineStr">
+      <c r="E38" s="23" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="F37" s="23" t="inlineStr">
+      <c r="F38" s="23" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="G37" s="24" t="inlineStr">
+      <c r="G38" s="24" t="inlineStr">
         <is>
           <t>配置が変わる場合は転送が必要</t>
         </is>
       </c>
-      <c r="H37" s="24" t="inlineStr">
+      <c r="H38" s="24" t="inlineStr">
         <is>
           <t>★GA現行に単独ページなし。「表示は現在と同様」とのご要望のため、現在の導線をご確認のうえ設計します</t>
         </is>
       </c>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="19" t="inlineStr">
-        <is>
-          <t>第1階層</t>
-        </is>
-      </c>
-      <c r="B38" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　プライバシーポリシー</t>
-        </is>
-      </c>
-      <c r="C38" s="21" t="inlineStr">
-        <is>
-          <t>https://www.glavisarchitects.com/privacy/</t>
-        </is>
-      </c>
-      <c r="D38" s="22" t="inlineStr">
-        <is>
-          <t>GAサイトから</t>
-        </is>
-      </c>
-      <c r="E38" s="19" t="inlineStr">
-        <is>
-          <t>確定</t>
-        </is>
-      </c>
-      <c r="F38" s="19" t="inlineStr">
-        <is>
-          <t>不要</t>
-        </is>
-      </c>
-      <c r="G38" s="20" t="inlineStr">
-        <is>
-          <t>GA既存。URL変更なし</t>
-        </is>
-      </c>
-      <c r="H38" s="20" t="inlineStr"/>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="14" t="inlineStr">
@@ -2351,12 +2355,12 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">　サイトポリシー</t>
+          <t xml:space="preserve">　プライバシーポリシー</t>
         </is>
       </c>
       <c r="C39" s="16" t="inlineStr">
         <is>
-          <t>https://www.glavisarchitects.com/site/</t>
+          <t>https://www.glavisarchitects.com/privacy/</t>
         </is>
       </c>
       <c r="D39" s="17" t="inlineStr">
@@ -2389,38 +2393,76 @@
       </c>
       <c r="B40" s="27" t="inlineStr">
         <is>
+          <t xml:space="preserve">　サイトポリシー</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com/site/</t>
+        </is>
+      </c>
+      <c r="D40" s="22" t="inlineStr">
+        <is>
+          <t>GAサイトから</t>
+        </is>
+      </c>
+      <c r="E40" s="19" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="F40" s="19" t="inlineStr">
+        <is>
+          <t>不要</t>
+        </is>
+      </c>
+      <c r="G40" s="20" t="inlineStr">
+        <is>
+          <t>GA既存。URL変更なし</t>
+        </is>
+      </c>
+      <c r="H40" s="20" t="inlineStr"/>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>第1階層</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="inlineStr">
+        <is>
           <t xml:space="preserve">　品質・情報セキュリティ基本方針</t>
         </is>
       </c>
-      <c r="C40" s="21" t="inlineStr">
+      <c r="C41" s="16" t="inlineStr">
         <is>
           <t>https://www.glavisarchitects.com/security/</t>
         </is>
       </c>
-      <c r="D40" s="22" t="inlineStr">
+      <c r="D41" s="17" t="inlineStr">
         <is>
           <t>GAサイトから</t>
         </is>
       </c>
-      <c r="E40" s="19" t="inlineStr">
+      <c r="E41" s="14" t="inlineStr">
         <is>
           <t>確定</t>
         </is>
       </c>
-      <c r="F40" s="19" t="inlineStr">
+      <c r="F41" s="14" t="inlineStr">
         <is>
           <t>不要</t>
         </is>
       </c>
-      <c r="G40" s="20" t="inlineStr">
+      <c r="G41" s="18" t="inlineStr">
         <is>
           <t>GA既存。URL変更なし</t>
         </is>
       </c>
-      <c r="H40" s="20" t="inlineStr"/>
+      <c r="H41" s="18" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H40"/>
+  <autoFilter ref="A3:H41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2431,7 +2473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2596,7 +2638,7 @@
           <t>https://www.glavis-hd.com/company/message/</t>
         </is>
       </c>
-      <c r="D6" s="32" t="inlineStr">
+      <c r="D6" s="40" t="inlineStr">
         <is>
           <t>HDサイトから</t>
         </is>
@@ -2676,7 +2718,7 @@
           <t>https://www.glavis-hd.com/recruit/</t>
         </is>
       </c>
-      <c r="D8" s="32" t="inlineStr">
+      <c r="D8" s="40" t="inlineStr">
         <is>
           <t>HDサイトから</t>
         </is>
@@ -2703,64 +2745,60 @@
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="23" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>第1階層</t>
         </is>
       </c>
-      <c r="B9" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　監修者・執筆者一覧</t>
-        </is>
-      </c>
-      <c r="C9" s="25" t="inlineStr">
-        <is>
-          <t>https://www.glavis-hd.com/author/</t>
-        </is>
-      </c>
-      <c r="D9" s="40" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　お問い合わせ・お申し込み</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/inquiry/</t>
+        </is>
+      </c>
+      <c r="D9" s="30" t="inlineStr">
         <is>
           <t>HDサイトから</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
         <is>
           <t>不要</t>
         </is>
       </c>
-      <c r="G9" s="24" t="inlineStr">
+      <c r="G9" s="18" t="inlineStr">
         <is>
           <t>HDに残置。URL変更なし</t>
         </is>
       </c>
-      <c r="H9" s="24" t="inlineStr">
-        <is>
-          <t>★8/10 方針変更で残置。17名分が1ページに並ぶ構成で、個人ページはありません。各記事からは /author/?author={ID} のクエリ付きURLで該当箇所へ遷移します</t>
-        </is>
-      </c>
+      <c r="H9" s="18" t="inlineStr"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="23" t="inlineStr">
         <is>
-          <t>第2階層</t>
-        </is>
-      </c>
-      <c r="B10" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　監修者 個別（アンカー）</t>
+          <t>第1階層</t>
+        </is>
+      </c>
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　採用お問い合わせ・エントリー</t>
         </is>
       </c>
       <c r="C10" s="25" t="inlineStr">
         <is>
-          <t>https://www.glavis-hd.com/author/?author={ID}</t>
-        </is>
-      </c>
-      <c r="D10" s="40" t="inlineStr">
+          <t>https://www.glavis-hd.com/inquiry_recruit/</t>
+        </is>
+      </c>
+      <c r="D10" s="31" t="inlineStr">
         <is>
           <t>HDサイトから</t>
         </is>
@@ -2782,7 +2820,7 @@
       </c>
       <c r="H10" s="24" t="inlineStr">
         <is>
-          <t>実体は上記1ページ内のアンカー（#author-{ID}）。全記事の「この記事の監修者」リンク先</t>
+          <t>採用サイトのGA移設にともない、HD側に残すか要確認</t>
         </is>
       </c>
     </row>
@@ -2794,12 +2832,12 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">　お問い合わせ・お申し込み</t>
+          <t xml:space="preserve">　プライバシーポリシー</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>https://www.glavis-hd.com/inquiry/</t>
+          <t>https://www.glavis-hd.com/privacy_policy/</t>
         </is>
       </c>
       <c r="D11" s="30" t="inlineStr">
@@ -2825,19 +2863,19 @@
       <c r="H11" s="18" t="inlineStr"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="23" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>第1階層</t>
         </is>
       </c>
-      <c r="B12" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　採用お問い合わせ・エントリー</t>
-        </is>
-      </c>
-      <c r="C12" s="25" t="inlineStr">
-        <is>
-          <t>https://www.glavis-hd.com/inquiry_recruit/</t>
+      <c r="B12" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　サイトポリシー</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>https://www.glavis-hd.com/site_policy/</t>
         </is>
       </c>
       <c r="D12" s="40" t="inlineStr">
@@ -2845,26 +2883,22 @@
           <t>HDサイトから</t>
         </is>
       </c>
-      <c r="E12" s="23" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F12" s="23" t="inlineStr">
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="F12" s="19" t="inlineStr">
         <is>
           <t>不要</t>
         </is>
       </c>
-      <c r="G12" s="24" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>HDに残置。URL変更なし</t>
         </is>
       </c>
-      <c r="H12" s="24" t="inlineStr">
-        <is>
-          <t>採用サイトのGA移設にともない、HD側に残すか要確認</t>
-        </is>
-      </c>
+      <c r="H12" s="20" t="inlineStr"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="14" t="inlineStr">
@@ -2874,12 +2908,12 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">　プライバシーポリシー</t>
+          <t xml:space="preserve">　ソーシャルメディアポリシー</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
-          <t>https://www.glavis-hd.com/privacy_policy/</t>
+          <t>https://www.glavis-hd.com/sns_policy/</t>
         </is>
       </c>
       <c r="D13" s="30" t="inlineStr">
@@ -2904,210 +2938,8 @@
       </c>
       <c r="H13" s="18" t="inlineStr"/>
     </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>第1階層</t>
-        </is>
-      </c>
-      <c r="B14" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　サイトポリシー</t>
-        </is>
-      </c>
-      <c r="C14" s="21" t="inlineStr">
-        <is>
-          <t>https://www.glavis-hd.com/site_policy/</t>
-        </is>
-      </c>
-      <c r="D14" s="32" t="inlineStr">
-        <is>
-          <t>HDサイトから</t>
-        </is>
-      </c>
-      <c r="E14" s="19" t="inlineStr">
-        <is>
-          <t>確定</t>
-        </is>
-      </c>
-      <c r="F14" s="19" t="inlineStr">
-        <is>
-          <t>不要</t>
-        </is>
-      </c>
-      <c r="G14" s="20" t="inlineStr">
-        <is>
-          <t>HDに残置。URL変更なし</t>
-        </is>
-      </c>
-      <c r="H14" s="20" t="inlineStr"/>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>第1階層</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　ソーシャルメディアポリシー</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>https://www.glavis-hd.com/sns_policy/</t>
-        </is>
-      </c>
-      <c r="D15" s="30" t="inlineStr">
-        <is>
-          <t>HDサイトから</t>
-        </is>
-      </c>
-      <c r="E15" s="14" t="inlineStr">
-        <is>
-          <t>確定</t>
-        </is>
-      </c>
-      <c r="F15" s="14" t="inlineStr">
-        <is>
-          <t>不要</t>
-        </is>
-      </c>
-      <c r="G15" s="18" t="inlineStr">
-        <is>
-          <t>HDに残置。URL変更なし</t>
-        </is>
-      </c>
-      <c r="H15" s="18" t="inlineStr"/>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="23" t="inlineStr">
-        <is>
-          <t>第1階層</t>
-        </is>
-      </c>
-      <c r="B16" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　社会問題への解決アプローチ</t>
-        </is>
-      </c>
-      <c r="C16" s="25" t="inlineStr">
-        <is>
-          <t>https://www.glavis-hd.com/case/</t>
-        </is>
-      </c>
-      <c r="D16" s="40" t="inlineStr">
-        <is>
-          <t>HDサイトから</t>
-        </is>
-      </c>
-      <c r="E16" s="23" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F16" s="23" t="inlineStr">
-        <is>
-          <t>不要</t>
-        </is>
-      </c>
-      <c r="G16" s="24" t="inlineStr">
-        <is>
-          <t>HDに残置。URL変更なし</t>
-        </is>
-      </c>
-      <c r="H16" s="24" t="inlineStr">
-        <is>
-          <t>★47記事はGAへ移行。一覧ページ自体を残すか、GAへ転送するか要確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="23" t="inlineStr">
-        <is>
-          <t>第1階層</t>
-        </is>
-      </c>
-      <c r="B17" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　日本の社会問題</t>
-        </is>
-      </c>
-      <c r="C17" s="25" t="inlineStr">
-        <is>
-          <t>https://www.glavis-hd.com/social_problem/</t>
-        </is>
-      </c>
-      <c r="D17" s="40" t="inlineStr">
-        <is>
-          <t>HDサイトから</t>
-        </is>
-      </c>
-      <c r="E17" s="23" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F17" s="23" t="inlineStr">
-        <is>
-          <t>不要</t>
-        </is>
-      </c>
-      <c r="G17" s="24" t="inlineStr">
-        <is>
-          <t>HDに残置。URL変更なし</t>
-        </is>
-      </c>
-      <c r="H17" s="24" t="inlineStr">
-        <is>
-          <t>★25記事はGAへ移行。インフォグラフィックDL導線の扱いを要確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="23" t="inlineStr">
-        <is>
-          <t>第2階層</t>
-        </is>
-      </c>
-      <c r="B18" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　インフォグラフィック一覧</t>
-        </is>
-      </c>
-      <c r="C18" s="25" t="inlineStr">
-        <is>
-          <t>https://www.glavis-hd.com/social_problem/download/</t>
-        </is>
-      </c>
-      <c r="D18" s="40" t="inlineStr">
-        <is>
-          <t>HDサイトから</t>
-        </is>
-      </c>
-      <c r="E18" s="23" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F18" s="23" t="inlineStr">
-        <is>
-          <t>不要</t>
-        </is>
-      </c>
-      <c r="G18" s="24" t="inlineStr">
-        <is>
-          <t>HDに残置。URL変更なし</t>
-        </is>
-      </c>
-      <c r="H18" s="24" t="inlineStr">
-        <is>
-          <t>DL申込フォーム・完了ページを含む4ページ。掲載先が決まり次第リダイレクト設定</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:H18"/>
+  <autoFilter ref="A3:H13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3418,7 +3250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3580,17 +3412,17 @@
       </c>
       <c r="B9" s="18" t="inlineStr">
         <is>
-          <t>HD「解決アプローチ」「日本の社会問題」一覧の扱い</t>
+          <t>監修者ページの扱い（ご指示の食い違い）</t>
         </is>
       </c>
       <c r="C9" s="18" t="inlineStr">
         <is>
-          <t>記事はGAへ移行しますが、一覧ページ自体をHDに残すか、GAへ転送するかで301リダイレクトの設定が変わります。</t>
+          <t>★8/10 大島様「HDに残す」／8/13 岡田様「GAへ移す」と、相反するご指示をいただいています。本図は8/13 岡田様のご判断（GAへ移しコンサルタントと同じ立ち位置）で作成しています。社内での最終確認をお願いいたします。</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>9/5</t>
+          <t>8/21 MTG②</t>
         </is>
       </c>
       <c r="E9" s="45" t="n"/>
@@ -3601,12 +3433,12 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>インフォグラフィックDL導線</t>
+          <t>GAコンサルタントページ未作成8名の扱い</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>HD「日本の社会問題」配下のDL申込・完了ページ4件をGA側へ移すか、HDに残すか。</t>
+          <t>★監修者17名のうちGA個人ページがあるのは7名のみです。GAへ統合するため、未作成8名（古見・光延・井上・根崎・内田・大塚貴・木場・鈴木）のページ作成要否のご判断が必要です。2名は他社（PTM／AmbiRise）で対象外と考えられます。</t>
         </is>
       </c>
       <c r="D10" s="19" t="inlineStr">
@@ -3622,17 +3454,17 @@
       </c>
       <c r="B11" s="18" t="inlineStr">
         <is>
-          <t>GA記事からの監修者リンクの向き先</t>
+          <t>インフォグラフィックDL導線の配置先</t>
         </is>
       </c>
       <c r="C11" s="18" t="inlineStr">
         <is>
-          <t>★現在、全記事の「この記事の監修者」は HD の /author/?author={ID} を指しています。記事がGAへ移った後もHDへ戻す動線のままでよいか、GAの「コンサルタント」ページへ向けるかをご判断ください。</t>
+          <t>GAへ移すことは決定済みです（8/13 岡田様）。GA側のどのURL配下に置くか（/agenda/download/ 等）をご確認ください。</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>9/5</t>
         </is>
       </c>
       <c r="E11" s="45" t="n"/>
@@ -3643,62 +3475,20 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>監修者17名とGAコンサルタントページの対応</t>
+          <t>GA「会社概要」「お問い合わせ」</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>★監修者17名のうち、GAに個人ページがあるのは7名のみです。8名はGAトップへのリンクのみ、2名は他社（PTM・AmbiRise）でした。GA側へ動線を寄せる場合、8名分のページ作成要否のご判断が必要です。</t>
+          <t>ラフ案に記載がありますがGA現行に単独ページが存在しません。新設するか、現在の導線のままとするかをご確認ください。</t>
         </is>
       </c>
       <c r="D12" s="19" t="inlineStr">
         <is>
-          <t>9/5</t>
+          <t>8/31</t>
         </is>
       </c>
       <c r="E12" s="45" t="n"/>
-    </row>
-    <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="14" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>クエリ文字列付きURLのリダイレクト</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>監修者リンクは /author/?author=38 のようにクエリ文字列で個人を指定しています。転送先を変える場合はクエリ単位の設定が必要になるため、方針決定後にITLINEで対応します。</t>
-        </is>
-      </c>
-      <c r="D13" s="14" t="inlineStr">
-        <is>
-          <t>9/20</t>
-        </is>
-      </c>
-      <c r="E13" s="45" t="n"/>
-    </row>
-    <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="19" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
-        <is>
-          <t>GA「会社概要」「お問い合わせ」</t>
-        </is>
-      </c>
-      <c r="C14" s="20" t="inlineStr">
-        <is>
-          <t>ラフ案に記載がありますがGA現行に単独ページが存在しません。新設するか、現在の導線のままとするかをご確認ください。</t>
-        </is>
-      </c>
-      <c r="D14" s="19" t="inlineStr">
-        <is>
-          <t>8/31</t>
-        </is>
-      </c>
-      <c r="E14" s="45" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3711,7 +3501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3769,98 +3559,120 @@
       </c>
       <c r="C4" s="20" t="inlineStr">
         <is>
-          <t>HDに残置し、GA「コンサルタント」は独立して整備</t>
+          <t>GAへ移しコンサルタントと同じ立ち位置に（ラフ案どおりに戻る）</t>
         </is>
       </c>
       <c r="D4" s="20" t="inlineStr">
         <is>
-          <t>8/10 大島様コメント「現在の監修者ページを残す運用に変更いたします」</t>
+          <t>8/13 岡田様ご判断。8/10 大島様の「HDに残す」から再変更</t>
         </is>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>グローバルナビ</t>
+          <t>HD「解決アプローチ」「日本の社会問題」一覧</t>
         </is>
       </c>
       <c r="B5" s="18" t="inlineStr">
         <is>
-          <t>8項目が並列</t>
+          <t>HDに残すか要確認</t>
         </is>
       </c>
       <c r="C5" s="18" t="inlineStr">
         <is>
-          <t>5〜6項目に集約（A案：メガメニュー型を推奨）</t>
+          <t>一覧・記事・インフォグラフィックDLとも、すべてGAへ移行</t>
         </is>
       </c>
       <c r="D5" s="18" t="inlineStr">
         <is>
-          <t>8/7 MTG「項目数が多く窮屈。まとめられる箇所は統合したい」</t>
+          <t>8/13 岡田様ご判断</t>
         </is>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="27" t="inlineStr">
         <is>
-          <t>サステナビリティ</t>
+          <t>グローバルナビ</t>
         </is>
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>ナビ直下（/sustainability/）</t>
+          <t>8項目が並列</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>企業情報内へ統合（要ご判断）</t>
+          <t>5〜6項目に集約（A案：メガメニュー型を推奨）</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
         <is>
-          <t>8/10 大島様コメント「企業情報内に統合することも検討しています」</t>
+          <t>8/7 MTG「項目数が多く窮屈。まとめられる箇所は統合したい」</t>
         </is>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>重点取り組み事項</t>
+          <t>サステナビリティ</t>
         </is>
       </c>
       <c r="B7" s="18" t="inlineStr">
         <is>
-          <t>「取り組み」表記</t>
+          <t>ナビ直下（/sustainability/）</t>
         </is>
       </c>
       <c r="C7" s="18" t="inlineStr">
         <is>
-          <t>「重点取組事項」へ修正</t>
+          <t>企業情報内へ統合（要ご判断）</t>
         </is>
       </c>
       <c r="D7" s="18" t="inlineStr">
         <is>
-          <t>8/10 伊藤様コメント（公用文表記：名詞は「取組」）</t>
+          <t>8/10 大島様コメント「企業情報内に統合することも検討しています」</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="27" t="inlineStr">
         <is>
+          <t>重点取り組み事項</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>「取り組み」表記</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>「重点取組事項」へ修正</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>8/10 伊藤様コメント（公用文表記：名詞は「取組」）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
           <t>採用サイトの事業内容</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>GA「事業内容」へ統合</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>今回はそのまま移設し、統合は次フェーズ・別予算</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr">
         <is>
           <t>8/7 MTG「リニューアルの色が濃くなるため次フェーズへ」</t>
         </is>

--- a/sitemap/glavis-sitemap-url-list.xlsx
+++ b/sitemap/glavis-sitemap-url-list.xlsx
@@ -16,7 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑥監修者とGAページ対応" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'①GAサイト'!$A$3:$H$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'①GAサイト'!$A$3:$H$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'②HDサイト'!$A$3:$H$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'⑥監修者とGAページ対応'!$A$3:$F$20</definedName>
   </definedNames>
@@ -764,7 +764,7 @@
     <row r="11">
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>①GAサイト　　　　新しいグラビス・アーキテクツのサイト構成（38行）</t>
+          <t>①GAサイト　　　　新しいグラビス・アーキテクツのサイト構成（40行）</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
     <row r="19">
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>・薄い黄色の行　… 状態が「要確認」。ご判断が必要な箇所です（全10件）</t>
+          <t>・薄い黄色の行　… 状態が「要確認」。ご判断が必要な箇所です（全11件）</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1863,188 +1863,192 @@
       </c>
       <c r="H26" s="20" t="inlineStr">
         <is>
-          <t>★8/13 岡田様ご判断により、HD「監修者・執筆者一覧」をGAへ移しコンサルタントへ統合する（8/10 大島様の「HDに残す」から再変更）</t>
+          <t>★8/13 岡田様ご判断により、HD「監修者・執筆者一覧」をGAへ移設。コンサルタント個人ページと並列に配置する（8/10 大島様の「HDに残す」から再変更）</t>
         </is>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="23" t="inlineStr">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>第2階層</t>
         </is>
       </c>
-      <c r="B27" s="24" t="inlineStr">
+      <c r="B27" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">　　コンサルタント（個人ページ）</t>
         </is>
       </c>
-      <c r="C27" s="25" t="inlineStr">
+      <c r="C27" s="16" t="inlineStr">
         <is>
           <t>https://www.glavisarchitects.com/member/{id}/</t>
         </is>
       </c>
-      <c r="D27" s="26" t="inlineStr">
+      <c r="D27" s="17" t="inlineStr">
         <is>
           <t>GAサイトから</t>
         </is>
       </c>
-      <c r="E27" s="23" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F27" s="23" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="G27" s="24" t="inlineStr">
-        <is>
-          <t>配置が変わる場合は転送が必要</t>
-        </is>
-      </c>
-      <c r="H27" s="24" t="inlineStr">
-        <is>
-          <t>★監修者17名と同じ立ち位置に揃える。GA個人ページがあるのは7名のみで、8名は未作成・2名は他社（PTM／AmbiRise）。未作成8名の扱いは要ご判断</t>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
+        <is>
+          <t>不要</t>
+        </is>
+      </c>
+      <c r="G27" s="18" t="inlineStr">
+        <is>
+          <t>GA既存。URL変更なし</t>
+        </is>
+      </c>
+      <c r="H27" s="18" t="inlineStr">
+        <is>
+          <t>GAに記事を掲載するコンサルメンバーは必ず紹介を掲載。現在7名分が作成済み</t>
         </is>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="23" t="inlineStr">
         <is>
+          <t>第2階層</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　監修者・執筆者一覧</t>
+        </is>
+      </c>
+      <c r="C28" s="25" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com/author/</t>
+        </is>
+      </c>
+      <c r="D28" s="31" t="inlineStr">
+        <is>
+          <t>HDサイトから</t>
+        </is>
+      </c>
+      <c r="E28" s="23" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F28" s="23" t="inlineStr">
+        <is>
+          <t>必要</t>
+        </is>
+      </c>
+      <c r="G28" s="24" t="inlineStr">
+        <is>
+          <t>旧：https://www.glavis-hd.com の該当ページからの転送</t>
+        </is>
+      </c>
+      <c r="H28" s="24" t="inlineStr">
+        <is>
+          <t>★HDから移設。17名が1ページに並ぶ構成で個人ページはなし。個人ページと並列に配置。GA配下でのURLは要確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>第3階層</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　監修者 個別（アンカー）</t>
+        </is>
+      </c>
+      <c r="C29" s="25" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com/author/?author={ID}</t>
+        </is>
+      </c>
+      <c r="D29" s="31" t="inlineStr">
+        <is>
+          <t>HDサイトから</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F29" s="23" t="inlineStr">
+        <is>
+          <t>必要</t>
+        </is>
+      </c>
+      <c r="G29" s="24" t="inlineStr">
+        <is>
+          <t>旧：https://www.glavis-hd.com の該当ページからの転送</t>
+        </is>
+      </c>
+      <c r="H29" s="24" t="inlineStr">
+        <is>
+          <t>実体は上記1ページ内のアンカー（#author-{ID}）。全記事の「この記事の監修者」リンク先。クエリ単位での転送設定が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="23" t="inlineStr">
+        <is>
           <t>第1階層</t>
         </is>
       </c>
-      <c r="B28" s="28" t="inlineStr">
+      <c r="B30" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">　ニュース</t>
         </is>
       </c>
-      <c r="C28" s="25" t="inlineStr">
+      <c r="C30" s="25" t="inlineStr">
         <is>
           <t>https://www.glavisarchitects.com/news/</t>
         </is>
       </c>
-      <c r="D28" s="29" t="inlineStr">
+      <c r="D30" s="29" t="inlineStr">
         <is>
           <t>新規ページ</t>
         </is>
       </c>
-      <c r="E28" s="23" t="inlineStr">
+      <c r="E30" s="23" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="F28" s="23" t="inlineStr">
+      <c r="F30" s="23" t="inlineStr">
         <is>
           <t>不要</t>
         </is>
       </c>
-      <c r="G28" s="24" t="inlineStr">
+      <c r="G30" s="24" t="inlineStr">
         <is>
           <t>新規ページのため旧URLなし</t>
         </is>
       </c>
-      <c r="H28" s="24" t="inlineStr">
+      <c r="H30" s="24" t="inlineStr">
         <is>
           <t>★GA現行にニュースページは存在しません（ラフ案では「GAサイトから」となっていますが要確認）。HDのニュース85件はHDに残る前提のため、GA側に新設するかどうかのご判断が必要</t>
         </is>
       </c>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="14" t="inlineStr">
-        <is>
-          <t>第1階層</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　採用情報</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>https://www.glavisarchitects.com/recruit/</t>
-        </is>
-      </c>
-      <c r="D29" s="33" t="inlineStr">
-        <is>
-          <t>採用サイトから</t>
-        </is>
-      </c>
-      <c r="E29" s="14" t="inlineStr">
-        <is>
-          <t>確定</t>
-        </is>
-      </c>
-      <c r="F29" s="14" t="inlineStr">
-        <is>
-          <t>必要</t>
-        </is>
-      </c>
-      <c r="G29" s="18" t="inlineStr">
-        <is>
-          <t>旧：https://www.glavis-hd.com/recruit/ga/… からの転送</t>
-        </is>
-      </c>
-      <c r="H29" s="18" t="inlineStr">
-        <is>
-          <t>HD配下からGA配下へ移設。301リダイレクト対象60ページ</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="19" t="inlineStr">
-        <is>
-          <t>第2階層</t>
-        </is>
-      </c>
-      <c r="B30" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　キャリア採用求人一覧</t>
-        </is>
-      </c>
-      <c r="C30" s="21" t="inlineStr">
-        <is>
-          <t>https://www.glavisarchitects.com/recruit/career_menu/</t>
-        </is>
-      </c>
-      <c r="D30" s="34" t="inlineStr">
-        <is>
-          <t>採用サイトから</t>
-        </is>
-      </c>
-      <c r="E30" s="19" t="inlineStr">
-        <is>
-          <t>確定</t>
-        </is>
-      </c>
-      <c r="F30" s="19" t="inlineStr">
-        <is>
-          <t>必要</t>
-        </is>
-      </c>
-      <c r="G30" s="20" t="inlineStr">
-        <is>
-          <t>旧：https://www.glavis-hd.com/recruit/ga/… からの転送</t>
-        </is>
-      </c>
-      <c r="H30" s="20" t="inlineStr"/>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="14" t="inlineStr">
         <is>
-          <t>第2階層</t>
-        </is>
-      </c>
-      <c r="B31" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　キャリア設計</t>
+          <t>第1階層</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　採用情報</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
         <is>
-          <t>https://www.glavisarchitects.com/recruit/careerplan/</t>
+          <t>https://www.glavisarchitects.com/recruit/</t>
         </is>
       </c>
       <c r="D31" s="33" t="inlineStr">
@@ -2067,7 +2071,11 @@
           <t>旧：https://www.glavis-hd.com/recruit/ga/… からの転送</t>
         </is>
       </c>
-      <c r="H31" s="18" t="inlineStr"/>
+      <c r="H31" s="18" t="inlineStr">
+        <is>
+          <t>HD配下からGA配下へ移設。301リダイレクト対象60ページ</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="19" t="inlineStr">
@@ -2077,12 +2085,12 @@
       </c>
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　はたらく環境</t>
+          <t xml:space="preserve">　　キャリア採用求人一覧</t>
         </is>
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>https://www.glavisarchitects.com/recruit/environment/</t>
+          <t>https://www.glavisarchitects.com/recruit/career_menu/</t>
         </is>
       </c>
       <c r="D32" s="34" t="inlineStr">
@@ -2115,12 +2123,12 @@
       </c>
       <c r="B33" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　はたらき方</t>
+          <t xml:space="preserve">　　キャリア設計</t>
         </is>
       </c>
       <c r="C33" s="16" t="inlineStr">
         <is>
-          <t>https://www.glavisarchitects.com/recruit/workstyle/</t>
+          <t>https://www.glavisarchitects.com/recruit/careerplan/</t>
         </is>
       </c>
       <c r="D33" s="33" t="inlineStr">
@@ -2153,12 +2161,12 @@
       </c>
       <c r="B34" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　社員紹介</t>
+          <t xml:space="preserve">　　はたらく環境</t>
         </is>
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>https://www.glavisarchitects.com/recruit/member/</t>
+          <t>https://www.glavisarchitects.com/recruit/environment/</t>
         </is>
       </c>
       <c r="D34" s="34" t="inlineStr">
@@ -2191,12 +2199,12 @@
       </c>
       <c r="B35" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　よくいただくご質問</t>
+          <t xml:space="preserve">　　はたらき方</t>
         </is>
       </c>
       <c r="C35" s="16" t="inlineStr">
         <is>
-          <t>https://www.glavisarchitects.com/recruit/faq/</t>
+          <t>https://www.glavisarchitects.com/recruit/workstyle/</t>
         </is>
       </c>
       <c r="D35" s="33" t="inlineStr">
@@ -2222,46 +2230,42 @@
       <c r="H35" s="18" t="inlineStr"/>
     </row>
     <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="35" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>第2階層</t>
         </is>
       </c>
-      <c r="B36" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　事業内容（採用）</t>
-        </is>
-      </c>
-      <c r="C36" s="37" t="inlineStr">
-        <is>
-          <t>https://www.glavisarchitects.com/recruit/ourwork/</t>
-        </is>
-      </c>
-      <c r="D36" s="38" t="inlineStr">
+      <c r="B36" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　社員紹介</t>
+        </is>
+      </c>
+      <c r="C36" s="21" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com/recruit/member/</t>
+        </is>
+      </c>
+      <c r="D36" s="34" t="inlineStr">
         <is>
           <t>採用サイトから</t>
         </is>
       </c>
-      <c r="E36" s="35" t="inlineStr">
-        <is>
-          <t>次フェーズ</t>
-        </is>
-      </c>
-      <c r="F36" s="35" t="inlineStr">
+      <c r="E36" s="19" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="F36" s="19" t="inlineStr">
         <is>
           <t>必要</t>
         </is>
       </c>
-      <c r="G36" s="36" t="inlineStr">
+      <c r="G36" s="20" t="inlineStr">
         <is>
           <t>旧：https://www.glavis-hd.com/recruit/ga/… からの転送</t>
         </is>
       </c>
-      <c r="H36" s="36" t="inlineStr">
-        <is>
-          <t>★GA「事業内容」との統合は次フェーズ・別予算。今回はそのまま移設</t>
-        </is>
-      </c>
+      <c r="H36" s="20" t="inlineStr"/>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="14" t="inlineStr">
@@ -2271,12 +2275,12 @@
       </c>
       <c r="B37" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　採用お問い合わせ</t>
+          <t xml:space="preserve">　　よくいただくご質問</t>
         </is>
       </c>
       <c r="C37" s="16" t="inlineStr">
         <is>
-          <t>https://www.glavisarchitects.com/recruit/inquiry/</t>
+          <t>https://www.glavisarchitects.com/recruit/faq/</t>
         </is>
       </c>
       <c r="D37" s="33" t="inlineStr">
@@ -2299,129 +2303,133 @@
           <t>旧：https://www.glavis-hd.com/recruit/ga/… からの転送</t>
         </is>
       </c>
-      <c r="H37" s="18" t="inlineStr">
-        <is>
-          <t>HD側フォームからの移設</t>
-        </is>
-      </c>
+      <c r="H37" s="18" t="inlineStr"/>
     </row>
     <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="23" t="inlineStr">
-        <is>
-          <t>第1階層</t>
-        </is>
-      </c>
-      <c r="B38" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　お問い合わせ</t>
-        </is>
-      </c>
-      <c r="C38" s="25" t="inlineStr">
-        <is>
-          <t>https://www.glavisarchitects.com/inquiry/</t>
-        </is>
-      </c>
-      <c r="D38" s="26" t="inlineStr">
-        <is>
-          <t>GAサイトから</t>
-        </is>
-      </c>
-      <c r="E38" s="23" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F38" s="23" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="G38" s="24" t="inlineStr">
-        <is>
-          <t>配置が変わる場合は転送が必要</t>
-        </is>
-      </c>
-      <c r="H38" s="24" t="inlineStr">
-        <is>
-          <t>★GA現行に単独ページなし。「表示は現在と同様」とのご要望のため、現在の導線をご確認のうえ設計します</t>
+      <c r="A38" s="35" t="inlineStr">
+        <is>
+          <t>第2階層</t>
+        </is>
+      </c>
+      <c r="B38" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　事業内容（採用）</t>
+        </is>
+      </c>
+      <c r="C38" s="37" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com/recruit/ourwork/</t>
+        </is>
+      </c>
+      <c r="D38" s="38" t="inlineStr">
+        <is>
+          <t>採用サイトから</t>
+        </is>
+      </c>
+      <c r="E38" s="35" t="inlineStr">
+        <is>
+          <t>次フェーズ</t>
+        </is>
+      </c>
+      <c r="F38" s="35" t="inlineStr">
+        <is>
+          <t>必要</t>
+        </is>
+      </c>
+      <c r="G38" s="36" t="inlineStr">
+        <is>
+          <t>旧：https://www.glavis-hd.com/recruit/ga/… からの転送</t>
+        </is>
+      </c>
+      <c r="H38" s="36" t="inlineStr">
+        <is>
+          <t>★GA「事業内容」との統合は次フェーズ・別予算。今回はそのまま移設</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="14" t="inlineStr">
         <is>
+          <t>第2階層</t>
+        </is>
+      </c>
+      <c r="B39" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　採用お問い合わせ</t>
+        </is>
+      </c>
+      <c r="C39" s="16" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com/recruit/inquiry/</t>
+        </is>
+      </c>
+      <c r="D39" s="33" t="inlineStr">
+        <is>
+          <t>採用サイトから</t>
+        </is>
+      </c>
+      <c r="E39" s="14" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="F39" s="14" t="inlineStr">
+        <is>
+          <t>必要</t>
+        </is>
+      </c>
+      <c r="G39" s="18" t="inlineStr">
+        <is>
+          <t>旧：https://www.glavis-hd.com/recruit/ga/… からの転送</t>
+        </is>
+      </c>
+      <c r="H39" s="18" t="inlineStr">
+        <is>
+          <t>HD側フォームからの移設</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="23" t="inlineStr">
+        <is>
           <t>第1階層</t>
         </is>
       </c>
-      <c r="B39" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　プライバシーポリシー</t>
-        </is>
-      </c>
-      <c r="C39" s="16" t="inlineStr">
-        <is>
-          <t>https://www.glavisarchitects.com/privacy/</t>
-        </is>
-      </c>
-      <c r="D39" s="17" t="inlineStr">
+      <c r="B40" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　お問い合わせ</t>
+        </is>
+      </c>
+      <c r="C40" s="25" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com/inquiry/</t>
+        </is>
+      </c>
+      <c r="D40" s="26" t="inlineStr">
         <is>
           <t>GAサイトから</t>
         </is>
       </c>
-      <c r="E39" s="14" t="inlineStr">
-        <is>
-          <t>確定</t>
-        </is>
-      </c>
-      <c r="F39" s="14" t="inlineStr">
-        <is>
-          <t>不要</t>
-        </is>
-      </c>
-      <c r="G39" s="18" t="inlineStr">
-        <is>
-          <t>GA既存。URL変更なし</t>
-        </is>
-      </c>
-      <c r="H39" s="18" t="inlineStr"/>
-    </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="19" t="inlineStr">
-        <is>
-          <t>第1階層</t>
-        </is>
-      </c>
-      <c r="B40" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　サイトポリシー</t>
-        </is>
-      </c>
-      <c r="C40" s="21" t="inlineStr">
-        <is>
-          <t>https://www.glavisarchitects.com/site/</t>
-        </is>
-      </c>
-      <c r="D40" s="22" t="inlineStr">
-        <is>
-          <t>GAサイトから</t>
-        </is>
-      </c>
-      <c r="E40" s="19" t="inlineStr">
-        <is>
-          <t>確定</t>
-        </is>
-      </c>
-      <c r="F40" s="19" t="inlineStr">
-        <is>
-          <t>不要</t>
-        </is>
-      </c>
-      <c r="G40" s="20" t="inlineStr">
-        <is>
-          <t>GA既存。URL変更なし</t>
-        </is>
-      </c>
-      <c r="H40" s="20" t="inlineStr"/>
+      <c r="E40" s="23" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F40" s="23" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="G40" s="24" t="inlineStr">
+        <is>
+          <t>配置が変わる場合は転送が必要</t>
+        </is>
+      </c>
+      <c r="H40" s="24" t="inlineStr">
+        <is>
+          <t>★GA現行に単独ページなし。「表示は現在と同様」とのご要望のため、現在の導線をご確認のうえ設計します</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="14" t="inlineStr">
@@ -2431,38 +2439,114 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
+          <t xml:space="preserve">　プライバシーポリシー</t>
+        </is>
+      </c>
+      <c r="C41" s="16" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com/privacy/</t>
+        </is>
+      </c>
+      <c r="D41" s="17" t="inlineStr">
+        <is>
+          <t>GAサイトから</t>
+        </is>
+      </c>
+      <c r="E41" s="14" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="F41" s="14" t="inlineStr">
+        <is>
+          <t>不要</t>
+        </is>
+      </c>
+      <c r="G41" s="18" t="inlineStr">
+        <is>
+          <t>GA既存。URL変更なし</t>
+        </is>
+      </c>
+      <c r="H41" s="18" t="inlineStr"/>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>第1階層</t>
+        </is>
+      </c>
+      <c r="B42" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　サイトポリシー</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com/site/</t>
+        </is>
+      </c>
+      <c r="D42" s="22" t="inlineStr">
+        <is>
+          <t>GAサイトから</t>
+        </is>
+      </c>
+      <c r="E42" s="19" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="F42" s="19" t="inlineStr">
+        <is>
+          <t>不要</t>
+        </is>
+      </c>
+      <c r="G42" s="20" t="inlineStr">
+        <is>
+          <t>GA既存。URL変更なし</t>
+        </is>
+      </c>
+      <c r="H42" s="20" t="inlineStr"/>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="14" t="inlineStr">
+        <is>
+          <t>第1階層</t>
+        </is>
+      </c>
+      <c r="B43" s="15" t="inlineStr">
+        <is>
           <t xml:space="preserve">　品質・情報セキュリティ基本方針</t>
         </is>
       </c>
-      <c r="C41" s="16" t="inlineStr">
+      <c r="C43" s="16" t="inlineStr">
         <is>
           <t>https://www.glavisarchitects.com/security/</t>
         </is>
       </c>
-      <c r="D41" s="17" t="inlineStr">
+      <c r="D43" s="17" t="inlineStr">
         <is>
           <t>GAサイトから</t>
         </is>
       </c>
-      <c r="E41" s="14" t="inlineStr">
+      <c r="E43" s="14" t="inlineStr">
         <is>
           <t>確定</t>
         </is>
       </c>
-      <c r="F41" s="14" t="inlineStr">
+      <c r="F43" s="14" t="inlineStr">
         <is>
           <t>不要</t>
         </is>
       </c>
-      <c r="G41" s="18" t="inlineStr">
+      <c r="G43" s="18" t="inlineStr">
         <is>
           <t>GA既存。URL変更なし</t>
         </is>
       </c>
-      <c r="H41" s="18" t="inlineStr"/>
+      <c r="H43" s="18" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H41"/>
+  <autoFilter ref="A3:H43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3417,7 +3501,7 @@
       </c>
       <c r="C9" s="18" t="inlineStr">
         <is>
-          <t>★8/10 大島様「HDに残す」／8/13 岡田様「GAへ移す」と、相反するご指示をいただいています。本図は8/13 岡田様のご判断（GAへ移しコンサルタントと同じ立ち位置）で作成しています。社内での最終確認をお願いいたします。</t>
+          <t>★8/10 大島様「HDに残す」／8/13 岡田様「GAへ移す」と、相反するご指示をいただいています。本図は8/13 岡田様のご判断（GAへ移設し、コンサルタント個人ページと並列に配置）で作成しています。社内での最終確認をお願いいたします。</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
@@ -3433,12 +3517,12 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>GAコンサルタントページ未作成8名の扱い</t>
+          <t>監修者一覧とコンサルタント個人ページの役割分担</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>★監修者17名のうちGA個人ページがあるのは7名のみです。GAへ統合するため、未作成8名（古見・光延・井上・根崎・内田・大塚貴・木場・鈴木）のページ作成要否のご判断が必要です。2名は他社（PTM／AmbiRise）で対象外と考えられます。</t>
+          <t>両方をコンサルタント配下に並列で置くため、掲載内容の重複が生じます。個人ページがあるのは17名中7名で、残り8名は一覧のみへの掲載となります（2名は他社のPTM／AmbiRise）。一覧から個人ページへの導線の有無とあわせてご確認ください。</t>
         </is>
       </c>
       <c r="D10" s="19" t="inlineStr">
@@ -3559,7 +3643,7 @@
       </c>
       <c r="C4" s="20" t="inlineStr">
         <is>
-          <t>GAへ移しコンサルタントと同じ立ち位置に（ラフ案どおりに戻る）</t>
+          <t>GAへ移設し、コンサルタント個人ページと並列に配置（統合はしない）</t>
         </is>
       </c>
       <c r="D4" s="20" t="inlineStr">

--- a/sitemap/glavis-sitemap-url-list.xlsx
+++ b/sitemap/glavis-sitemap-url-list.xlsx
@@ -16,7 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑥監修者とGAページ対応" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'①GAサイト'!$A$3:$H$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'①GAサイト'!$A$3:$H$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'②HDサイト'!$A$3:$H$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'⑥監修者とGAページ対応'!$A$3:$F$20</definedName>
   </definedNames>
@@ -287,13 +287,16 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -309,9 +312,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -764,7 +764,7 @@
     <row r="11">
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>①GAサイト　　　　新しいグラビス・アーキテクツのサイト構成（40行）</t>
+          <t>①GAサイト　　　　新しいグラビス・アーキテクツのサイト構成（41行）</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　Case Study（事例）</t>
+          <t xml:space="preserve">　　Case Study（事例・GA既存分）</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -1619,71 +1619,71 @@
       </c>
       <c r="H20" s="20" t="inlineStr">
         <is>
-          <t>GA既存の事例27件＋HD「解決アプローチ」47記事の移行先</t>
+          <t>GAサイトに現在ある事例27件。URL変更なし</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="23" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>第2階層</t>
         </is>
       </c>
-      <c r="B21" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　インフォグラフィック一覧</t>
-        </is>
-      </c>
-      <c r="C21" s="25" t="inlineStr">
-        <is>
-          <t>https://www.glavisarchitects.com/agenda/download/</t>
-        </is>
-      </c>
-      <c r="D21" s="31" t="inlineStr">
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　Case Study（事例・HDからの移行分）</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com/case/{id}/</t>
+        </is>
+      </c>
+      <c r="D21" s="30" t="inlineStr">
         <is>
           <t>HDサイトから</t>
         </is>
       </c>
-      <c r="E21" s="23" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F21" s="23" t="inlineStr">
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="inlineStr">
         <is>
           <t>必要</t>
         </is>
       </c>
-      <c r="G21" s="24" t="inlineStr">
+      <c r="G21" s="18" t="inlineStr">
         <is>
           <t>旧：https://www.glavis-hd.com の該当ページからの転送</t>
         </is>
       </c>
-      <c r="H21" s="24" t="inlineStr">
-        <is>
-          <t>★8/13 岡田様ご判断によりGAへ移行。HD /social_problem/download/ のDL申込フォーム・完了ページを含む4ページ。配置先URLは要確認</t>
+      <c r="H21" s="18" t="inlineStr">
+        <is>
+          <t>HD「社会問題への解決アプローチ」47記事の移行先。301リダイレクトの対象</t>
         </is>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="23" t="inlineStr">
         <is>
-          <t>第1階層</t>
-        </is>
-      </c>
-      <c r="B22" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　お客様</t>
+          <t>第2階層</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　インフォグラフィック一覧</t>
         </is>
       </c>
       <c r="C22" s="25" t="inlineStr">
         <is>
-          <t>https://www.glavisarchitects.com/customer/</t>
-        </is>
-      </c>
-      <c r="D22" s="29" t="inlineStr">
-        <is>
-          <t>新規ページ</t>
+          <t>https://www.glavisarchitects.com/agenda/download/</t>
+        </is>
+      </c>
+      <c r="D22" s="31" t="inlineStr">
+        <is>
+          <t>HDサイトから</t>
         </is>
       </c>
       <c r="E22" s="23" t="inlineStr">
@@ -1693,119 +1693,119 @@
       </c>
       <c r="F22" s="23" t="inlineStr">
         <is>
-          <t>不要</t>
+          <t>必要</t>
         </is>
       </c>
       <c r="G22" s="24" t="inlineStr">
         <is>
-          <t>新規ページのため旧URLなし</t>
+          <t>旧：https://www.glavis-hd.com の該当ページからの転送</t>
         </is>
       </c>
       <c r="H22" s="24" t="inlineStr">
         <is>
-          <t>★新設・準備中。記事の実体は今後グラビス様にてご用意。名称未定</t>
+          <t>★8/13 岡田様ご判断によりGAへ移行。HD /social_problem/download/ のDL申込フォーム・完了ページを含む4ページ。配置先URLは要確認</t>
         </is>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="23" t="inlineStr">
         <is>
+          <t>第1階層</t>
+        </is>
+      </c>
+      <c r="B23" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　お客様</t>
+        </is>
+      </c>
+      <c r="C23" s="25" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com/customer/</t>
+        </is>
+      </c>
+      <c r="D23" s="29" t="inlineStr">
+        <is>
+          <t>新規ページ</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F23" s="23" t="inlineStr">
+        <is>
+          <t>不要</t>
+        </is>
+      </c>
+      <c r="G23" s="24" t="inlineStr">
+        <is>
+          <t>新規ページのため旧URLなし</t>
+        </is>
+      </c>
+      <c r="H23" s="24" t="inlineStr">
+        <is>
+          <t>★新設・準備中。記事の実体は今後グラビス様にてご用意。名称未定</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="23" t="inlineStr">
+        <is>
           <t>第2階層</t>
         </is>
       </c>
-      <c r="B23" s="24" t="inlineStr">
+      <c r="B24" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">　　お客様（記事）</t>
         </is>
       </c>
-      <c r="C23" s="25" t="inlineStr">
+      <c r="C24" s="25" t="inlineStr">
         <is>
           <t>https://www.glavisarchitects.com/customer/{id}/</t>
         </is>
       </c>
-      <c r="D23" s="29" t="inlineStr">
+      <c r="D24" s="29" t="inlineStr">
         <is>
           <t>新規ページ</t>
         </is>
       </c>
-      <c r="E23" s="23" t="inlineStr">
+      <c r="E24" s="23" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="F23" s="23" t="inlineStr">
+      <c r="F24" s="23" t="inlineStr">
         <is>
           <t>不要</t>
         </is>
       </c>
-      <c r="G23" s="24" t="inlineStr">
+      <c r="G24" s="24" t="inlineStr">
         <is>
           <t>新規ページのため旧URLなし</t>
         </is>
       </c>
-      <c r="H23" s="24" t="inlineStr"/>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>第1階層</t>
-        </is>
-      </c>
-      <c r="B24" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　有識者インタビュー</t>
-        </is>
-      </c>
-      <c r="C24" s="21" t="inlineStr">
-        <is>
-          <t>https://www.glavisarchitects.com/interview/</t>
-        </is>
-      </c>
-      <c r="D24" s="32" t="inlineStr">
-        <is>
-          <t>新規ページ</t>
-        </is>
-      </c>
-      <c r="E24" s="19" t="inlineStr">
-        <is>
-          <t>確定</t>
-        </is>
-      </c>
-      <c r="F24" s="19" t="inlineStr">
-        <is>
-          <t>不要</t>
-        </is>
-      </c>
-      <c r="G24" s="20" t="inlineStr">
-        <is>
-          <t>新規ページのため旧URLなし</t>
-        </is>
-      </c>
-      <c r="H24" s="20" t="inlineStr">
-        <is>
-          <t>★新設。HD「解決アプローチ＞対談」の記事を移行</t>
-        </is>
-      </c>
+      <c r="H24" s="24" t="inlineStr"/>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>第2階層</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　有識者インタビュー（記事）</t>
+          <t>第1階層</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　有識者インタビュー</t>
         </is>
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>https://www.glavisarchitects.com/interview/{id}/</t>
-        </is>
-      </c>
-      <c r="D25" s="30" t="inlineStr">
-        <is>
-          <t>HDサイトから</t>
+          <t>https://www.glavisarchitects.com/interview/</t>
+        </is>
+      </c>
+      <c r="D25" s="32" t="inlineStr">
+        <is>
+          <t>新規ページ</t>
         </is>
       </c>
       <c r="E25" s="14" t="inlineStr">
@@ -1815,35 +1815,39 @@
       </c>
       <c r="F25" s="14" t="inlineStr">
         <is>
-          <t>必要</t>
+          <t>不要</t>
         </is>
       </c>
       <c r="G25" s="18" t="inlineStr">
         <is>
-          <t>旧：https://www.glavis-hd.com の該当ページからの転送</t>
-        </is>
-      </c>
-      <c r="H25" s="18" t="inlineStr"/>
+          <t>新規ページのため旧URLなし</t>
+        </is>
+      </c>
+      <c r="H25" s="18" t="inlineStr">
+        <is>
+          <t>★新設。HD「解決アプローチ＞対談」の記事を移行</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="19" t="inlineStr">
         <is>
-          <t>第1階層</t>
-        </is>
-      </c>
-      <c r="B26" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　コンサルタント</t>
+          <t>第2階層</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　有識者インタビュー（記事）</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>https://www.glavisarchitects.com/member/</t>
-        </is>
-      </c>
-      <c r="D26" s="22" t="inlineStr">
-        <is>
-          <t>GAサイトから</t>
+          <t>https://www.glavisarchitects.com/interview/{id}/</t>
+        </is>
+      </c>
+      <c r="D26" s="33" t="inlineStr">
+        <is>
+          <t>HDサイトから</t>
         </is>
       </c>
       <c r="E26" s="19" t="inlineStr">
@@ -1853,118 +1857,114 @@
       </c>
       <c r="F26" s="19" t="inlineStr">
         <is>
-          <t>不要</t>
+          <t>必要</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
         <is>
-          <t>GA既存。URL変更なし</t>
-        </is>
-      </c>
-      <c r="H26" s="20" t="inlineStr">
-        <is>
-          <t>★8/13 岡田様ご判断により、HD「監修者・執筆者一覧」をGAへ移設。コンサルタント個人ページと並列に配置する（8/10 大島様の「HDに残す」から再変更）</t>
-        </is>
-      </c>
+          <t>旧：https://www.glavis-hd.com の該当ページからの転送</t>
+        </is>
+      </c>
+      <c r="H26" s="20" t="inlineStr"/>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="14" t="inlineStr">
         <is>
+          <t>第1階層</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　コンサルタント</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com/member/</t>
+        </is>
+      </c>
+      <c r="D27" s="17" t="inlineStr">
+        <is>
+          <t>GAサイトから</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
+        <is>
+          <t>不要</t>
+        </is>
+      </c>
+      <c r="G27" s="18" t="inlineStr">
+        <is>
+          <t>GA既存。URL変更なし</t>
+        </is>
+      </c>
+      <c r="H27" s="18" t="inlineStr">
+        <is>
+          <t>★8/13 岡田様ご判断により、HD「監修者・執筆者一覧」をGAへ移設。コンサルタント個人ページと並列に配置する（8/10 大島様の「HDに残す」から再変更）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
           <t>第2階層</t>
         </is>
       </c>
-      <c r="B27" s="18" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">　　コンサルタント（個人ページ）</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>https://www.glavisarchitects.com/member/{id}/</t>
         </is>
       </c>
-      <c r="D27" s="17" t="inlineStr">
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>GAサイトから</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
+      <c r="E28" s="19" t="inlineStr">
         <is>
           <t>確定</t>
         </is>
       </c>
-      <c r="F27" s="14" t="inlineStr">
+      <c r="F28" s="19" t="inlineStr">
         <is>
           <t>不要</t>
         </is>
       </c>
-      <c r="G27" s="18" t="inlineStr">
+      <c r="G28" s="20" t="inlineStr">
         <is>
           <t>GA既存。URL変更なし</t>
         </is>
       </c>
-      <c r="H27" s="18" t="inlineStr">
+      <c r="H28" s="20" t="inlineStr">
         <is>
           <t>GAに記事を掲載するコンサルメンバーは必ず紹介を掲載。現在7名分が作成済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="23" t="inlineStr">
-        <is>
-          <t>第2階層</t>
-        </is>
-      </c>
-      <c r="B28" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　監修者・執筆者一覧</t>
-        </is>
-      </c>
-      <c r="C28" s="25" t="inlineStr">
-        <is>
-          <t>https://www.glavisarchitects.com/author/</t>
-        </is>
-      </c>
-      <c r="D28" s="31" t="inlineStr">
-        <is>
-          <t>HDサイトから</t>
-        </is>
-      </c>
-      <c r="E28" s="23" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="F28" s="23" t="inlineStr">
-        <is>
-          <t>必要</t>
-        </is>
-      </c>
-      <c r="G28" s="24" t="inlineStr">
-        <is>
-          <t>旧：https://www.glavis-hd.com の該当ページからの転送</t>
-        </is>
-      </c>
-      <c r="H28" s="24" t="inlineStr">
-        <is>
-          <t>★HDから移設。17名が1ページに並ぶ構成で個人ページはなし。個人ページと並列に配置。GA配下でのURLは要確認</t>
         </is>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="23" t="inlineStr">
         <is>
-          <t>第3階層</t>
+          <t>第2階層</t>
         </is>
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　監修者 個別（アンカー）</t>
+          <t xml:space="preserve">　　監修者・執筆者一覧</t>
         </is>
       </c>
       <c r="C29" s="25" t="inlineStr">
         <is>
-          <t>https://www.glavisarchitects.com/author/?author={ID}</t>
+          <t>https://www.glavisarchitects.com/author/</t>
         </is>
       </c>
       <c r="D29" s="31" t="inlineStr">
@@ -1989,108 +1989,108 @@
       </c>
       <c r="H29" s="24" t="inlineStr">
         <is>
-          <t>実体は上記1ページ内のアンカー（#author-{ID}）。全記事の「この記事の監修者」リンク先。クエリ単位での転送設定が必要</t>
+          <t>★HDから移設。17名が1ページに並ぶ構成で個人ページはなし。個人ページと並列に配置。GA配下でのURLは要確認</t>
         </is>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="23" t="inlineStr">
         <is>
+          <t>第3階層</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　監修者 個別（アンカー）</t>
+        </is>
+      </c>
+      <c r="C30" s="25" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com/author/?author={ID}</t>
+        </is>
+      </c>
+      <c r="D30" s="31" t="inlineStr">
+        <is>
+          <t>HDサイトから</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
+          <t>必要</t>
+        </is>
+      </c>
+      <c r="G30" s="24" t="inlineStr">
+        <is>
+          <t>旧：https://www.glavis-hd.com の該当ページからの転送</t>
+        </is>
+      </c>
+      <c r="H30" s="24" t="inlineStr">
+        <is>
+          <t>実体は上記1ページ内のアンカー（#author-{ID}）。全記事の「この記事の監修者」リンク先。クエリ単位での転送設定が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="23" t="inlineStr">
+        <is>
           <t>第1階層</t>
         </is>
       </c>
-      <c r="B30" s="28" t="inlineStr">
+      <c r="B31" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">　ニュース</t>
         </is>
       </c>
-      <c r="C30" s="25" t="inlineStr">
+      <c r="C31" s="25" t="inlineStr">
         <is>
           <t>https://www.glavisarchitects.com/news/</t>
         </is>
       </c>
-      <c r="D30" s="29" t="inlineStr">
+      <c r="D31" s="29" t="inlineStr">
         <is>
           <t>新規ページ</t>
         </is>
       </c>
-      <c r="E30" s="23" t="inlineStr">
+      <c r="E31" s="23" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="F30" s="23" t="inlineStr">
+      <c r="F31" s="23" t="inlineStr">
         <is>
           <t>不要</t>
         </is>
       </c>
-      <c r="G30" s="24" t="inlineStr">
+      <c r="G31" s="24" t="inlineStr">
         <is>
           <t>新規ページのため旧URLなし</t>
         </is>
       </c>
-      <c r="H30" s="24" t="inlineStr">
+      <c r="H31" s="24" t="inlineStr">
         <is>
           <t>★GA現行にニュースページは存在しません（ラフ案では「GAサイトから」となっていますが要確認）。HDのニュース85件はHDに残る前提のため、GA側に新設するかどうかのご判断が必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="14" t="inlineStr">
-        <is>
-          <t>第1階層</t>
-        </is>
-      </c>
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　採用情報</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>https://www.glavisarchitects.com/recruit/</t>
-        </is>
-      </c>
-      <c r="D31" s="33" t="inlineStr">
-        <is>
-          <t>採用サイトから</t>
-        </is>
-      </c>
-      <c r="E31" s="14" t="inlineStr">
-        <is>
-          <t>確定</t>
-        </is>
-      </c>
-      <c r="F31" s="14" t="inlineStr">
-        <is>
-          <t>必要</t>
-        </is>
-      </c>
-      <c r="G31" s="18" t="inlineStr">
-        <is>
-          <t>旧：https://www.glavis-hd.com/recruit/ga/… からの転送</t>
-        </is>
-      </c>
-      <c r="H31" s="18" t="inlineStr">
-        <is>
-          <t>HD配下からGA配下へ移設。301リダイレクト対象60ページ</t>
         </is>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="19" t="inlineStr">
         <is>
-          <t>第2階層</t>
-        </is>
-      </c>
-      <c r="B32" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　キャリア採用求人一覧</t>
+          <t>第1階層</t>
+        </is>
+      </c>
+      <c r="B32" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　採用情報</t>
         </is>
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>https://www.glavisarchitects.com/recruit/career_menu/</t>
+          <t>https://www.glavisarchitects.com/recruit/</t>
         </is>
       </c>
       <c r="D32" s="34" t="inlineStr">
@@ -2113,7 +2113,11 @@
           <t>旧：https://www.glavis-hd.com/recruit/ga/… からの転送</t>
         </is>
       </c>
-      <c r="H32" s="20" t="inlineStr"/>
+      <c r="H32" s="20" t="inlineStr">
+        <is>
+          <t>HD配下からGA配下へ移設。301リダイレクト対象60ページ</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="14" t="inlineStr">
@@ -2123,15 +2127,15 @@
       </c>
       <c r="B33" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　キャリア設計</t>
+          <t xml:space="preserve">　　キャリア採用求人一覧</t>
         </is>
       </c>
       <c r="C33" s="16" t="inlineStr">
         <is>
-          <t>https://www.glavisarchitects.com/recruit/careerplan/</t>
-        </is>
-      </c>
-      <c r="D33" s="33" t="inlineStr">
+          <t>https://www.glavisarchitects.com/recruit/career_menu/</t>
+        </is>
+      </c>
+      <c r="D33" s="35" t="inlineStr">
         <is>
           <t>採用サイトから</t>
         </is>
@@ -2161,12 +2165,12 @@
       </c>
       <c r="B34" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　はたらく環境</t>
+          <t xml:space="preserve">　　キャリア設計</t>
         </is>
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>https://www.glavisarchitects.com/recruit/environment/</t>
+          <t>https://www.glavisarchitects.com/recruit/careerplan/</t>
         </is>
       </c>
       <c r="D34" s="34" t="inlineStr">
@@ -2199,15 +2203,15 @@
       </c>
       <c r="B35" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　はたらき方</t>
+          <t xml:space="preserve">　　はたらく環境</t>
         </is>
       </c>
       <c r="C35" s="16" t="inlineStr">
         <is>
-          <t>https://www.glavisarchitects.com/recruit/workstyle/</t>
-        </is>
-      </c>
-      <c r="D35" s="33" t="inlineStr">
+          <t>https://www.glavisarchitects.com/recruit/environment/</t>
+        </is>
+      </c>
+      <c r="D35" s="35" t="inlineStr">
         <is>
           <t>採用サイトから</t>
         </is>
@@ -2237,12 +2241,12 @@
       </c>
       <c r="B36" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　社員紹介</t>
+          <t xml:space="preserve">　　はたらき方</t>
         </is>
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>https://www.glavisarchitects.com/recruit/member/</t>
+          <t>https://www.glavisarchitects.com/recruit/workstyle/</t>
         </is>
       </c>
       <c r="D36" s="34" t="inlineStr">
@@ -2275,199 +2279,199 @@
       </c>
       <c r="B37" s="18" t="inlineStr">
         <is>
+          <t xml:space="preserve">　　社員紹介</t>
+        </is>
+      </c>
+      <c r="C37" s="16" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com/recruit/member/</t>
+        </is>
+      </c>
+      <c r="D37" s="35" t="inlineStr">
+        <is>
+          <t>採用サイトから</t>
+        </is>
+      </c>
+      <c r="E37" s="14" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="F37" s="14" t="inlineStr">
+        <is>
+          <t>必要</t>
+        </is>
+      </c>
+      <c r="G37" s="18" t="inlineStr">
+        <is>
+          <t>旧：https://www.glavis-hd.com/recruit/ga/… からの転送</t>
+        </is>
+      </c>
+      <c r="H37" s="18" t="inlineStr"/>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>第2階層</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
+        <is>
           <t xml:space="preserve">　　よくいただくご質問</t>
         </is>
       </c>
-      <c r="C37" s="16" t="inlineStr">
+      <c r="C38" s="21" t="inlineStr">
         <is>
           <t>https://www.glavisarchitects.com/recruit/faq/</t>
         </is>
       </c>
-      <c r="D37" s="33" t="inlineStr">
+      <c r="D38" s="34" t="inlineStr">
         <is>
           <t>採用サイトから</t>
         </is>
       </c>
-      <c r="E37" s="14" t="inlineStr">
+      <c r="E38" s="19" t="inlineStr">
         <is>
           <t>確定</t>
         </is>
       </c>
-      <c r="F37" s="14" t="inlineStr">
+      <c r="F38" s="19" t="inlineStr">
         <is>
           <t>必要</t>
         </is>
       </c>
-      <c r="G37" s="18" t="inlineStr">
+      <c r="G38" s="20" t="inlineStr">
         <is>
           <t>旧：https://www.glavis-hd.com/recruit/ga/… からの転送</t>
         </is>
       </c>
-      <c r="H37" s="18" t="inlineStr"/>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="35" t="inlineStr">
+      <c r="H38" s="20" t="inlineStr"/>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="36" t="inlineStr">
         <is>
           <t>第2階層</t>
         </is>
       </c>
-      <c r="B38" s="36" t="inlineStr">
+      <c r="B39" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">　　事業内容（採用）</t>
         </is>
       </c>
-      <c r="C38" s="37" t="inlineStr">
+      <c r="C39" s="38" t="inlineStr">
         <is>
           <t>https://www.glavisarchitects.com/recruit/ourwork/</t>
         </is>
       </c>
-      <c r="D38" s="38" t="inlineStr">
+      <c r="D39" s="39" t="inlineStr">
         <is>
           <t>採用サイトから</t>
         </is>
       </c>
-      <c r="E38" s="35" t="inlineStr">
+      <c r="E39" s="36" t="inlineStr">
         <is>
           <t>次フェーズ</t>
         </is>
       </c>
-      <c r="F38" s="35" t="inlineStr">
+      <c r="F39" s="36" t="inlineStr">
         <is>
           <t>必要</t>
         </is>
       </c>
-      <c r="G38" s="36" t="inlineStr">
+      <c r="G39" s="37" t="inlineStr">
         <is>
           <t>旧：https://www.glavis-hd.com/recruit/ga/… からの転送</t>
         </is>
       </c>
-      <c r="H38" s="36" t="inlineStr">
+      <c r="H39" s="37" t="inlineStr">
         <is>
           <t>★GA「事業内容」との統合は次フェーズ・別予算。今回はそのまま移設</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="14" t="inlineStr">
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>第2階層</t>
         </is>
       </c>
-      <c r="B39" s="18" t="inlineStr">
+      <c r="B40" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">　　採用お問い合わせ</t>
         </is>
       </c>
-      <c r="C39" s="16" t="inlineStr">
+      <c r="C40" s="21" t="inlineStr">
         <is>
           <t>https://www.glavisarchitects.com/recruit/inquiry/</t>
         </is>
       </c>
-      <c r="D39" s="33" t="inlineStr">
+      <c r="D40" s="34" t="inlineStr">
         <is>
           <t>採用サイトから</t>
         </is>
       </c>
-      <c r="E39" s="14" t="inlineStr">
+      <c r="E40" s="19" t="inlineStr">
         <is>
           <t>確定</t>
         </is>
       </c>
-      <c r="F39" s="14" t="inlineStr">
+      <c r="F40" s="19" t="inlineStr">
         <is>
           <t>必要</t>
         </is>
       </c>
-      <c r="G39" s="18" t="inlineStr">
+      <c r="G40" s="20" t="inlineStr">
         <is>
           <t>旧：https://www.glavis-hd.com/recruit/ga/… からの転送</t>
         </is>
       </c>
-      <c r="H39" s="18" t="inlineStr">
+      <c r="H40" s="20" t="inlineStr">
         <is>
           <t>HD側フォームからの移設</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="23" t="inlineStr">
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="23" t="inlineStr">
         <is>
           <t>第1階層</t>
         </is>
       </c>
-      <c r="B40" s="28" t="inlineStr">
+      <c r="B41" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">　お問い合わせ</t>
         </is>
       </c>
-      <c r="C40" s="25" t="inlineStr">
+      <c r="C41" s="25" t="inlineStr">
         <is>
           <t>https://www.glavisarchitects.com/inquiry/</t>
         </is>
       </c>
-      <c r="D40" s="26" t="inlineStr">
+      <c r="D41" s="26" t="inlineStr">
         <is>
           <t>GAサイトから</t>
         </is>
       </c>
-      <c r="E40" s="23" t="inlineStr">
+      <c r="E41" s="23" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="F40" s="23" t="inlineStr">
+      <c r="F41" s="23" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="G40" s="24" t="inlineStr">
+      <c r="G41" s="24" t="inlineStr">
         <is>
           <t>配置が変わる場合は転送が必要</t>
         </is>
       </c>
-      <c r="H40" s="24" t="inlineStr">
+      <c r="H41" s="24" t="inlineStr">
         <is>
           <t>★GA現行に単独ページなし。「表示は現在と同様」とのご要望のため、現在の導線をご確認のうえ設計します</t>
         </is>
       </c>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="14" t="inlineStr">
-        <is>
-          <t>第1階層</t>
-        </is>
-      </c>
-      <c r="B41" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　プライバシーポリシー</t>
-        </is>
-      </c>
-      <c r="C41" s="16" t="inlineStr">
-        <is>
-          <t>https://www.glavisarchitects.com/privacy/</t>
-        </is>
-      </c>
-      <c r="D41" s="17" t="inlineStr">
-        <is>
-          <t>GAサイトから</t>
-        </is>
-      </c>
-      <c r="E41" s="14" t="inlineStr">
-        <is>
-          <t>確定</t>
-        </is>
-      </c>
-      <c r="F41" s="14" t="inlineStr">
-        <is>
-          <t>不要</t>
-        </is>
-      </c>
-      <c r="G41" s="18" t="inlineStr">
-        <is>
-          <t>GA既存。URL変更なし</t>
-        </is>
-      </c>
-      <c r="H41" s="18" t="inlineStr"/>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="19" t="inlineStr">
@@ -2477,12 +2481,12 @@
       </c>
       <c r="B42" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">　サイトポリシー</t>
+          <t xml:space="preserve">　プライバシーポリシー</t>
         </is>
       </c>
       <c r="C42" s="21" t="inlineStr">
         <is>
-          <t>https://www.glavisarchitects.com/site/</t>
+          <t>https://www.glavisarchitects.com/privacy/</t>
         </is>
       </c>
       <c r="D42" s="22" t="inlineStr">
@@ -2515,38 +2519,76 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
+          <t xml:space="preserve">　サイトポリシー</t>
+        </is>
+      </c>
+      <c r="C43" s="16" t="inlineStr">
+        <is>
+          <t>https://www.glavisarchitects.com/site/</t>
+        </is>
+      </c>
+      <c r="D43" s="17" t="inlineStr">
+        <is>
+          <t>GAサイトから</t>
+        </is>
+      </c>
+      <c r="E43" s="14" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="F43" s="14" t="inlineStr">
+        <is>
+          <t>不要</t>
+        </is>
+      </c>
+      <c r="G43" s="18" t="inlineStr">
+        <is>
+          <t>GA既存。URL変更なし</t>
+        </is>
+      </c>
+      <c r="H43" s="18" t="inlineStr"/>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>第1階層</t>
+        </is>
+      </c>
+      <c r="B44" s="27" t="inlineStr">
+        <is>
           <t xml:space="preserve">　品質・情報セキュリティ基本方針</t>
         </is>
       </c>
-      <c r="C43" s="16" t="inlineStr">
+      <c r="C44" s="21" t="inlineStr">
         <is>
           <t>https://www.glavisarchitects.com/security/</t>
         </is>
       </c>
-      <c r="D43" s="17" t="inlineStr">
+      <c r="D44" s="22" t="inlineStr">
         <is>
           <t>GAサイトから</t>
         </is>
       </c>
-      <c r="E43" s="14" t="inlineStr">
+      <c r="E44" s="19" t="inlineStr">
         <is>
           <t>確定</t>
         </is>
       </c>
-      <c r="F43" s="14" t="inlineStr">
+      <c r="F44" s="19" t="inlineStr">
         <is>
           <t>不要</t>
         </is>
       </c>
-      <c r="G43" s="18" t="inlineStr">
+      <c r="G44" s="20" t="inlineStr">
         <is>
           <t>GA既存。URL変更なし</t>
         </is>
       </c>
-      <c r="H43" s="18" t="inlineStr"/>
+      <c r="H44" s="20" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H43"/>
+  <autoFilter ref="A3:H44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2642,7 +2684,7 @@
           <t>https://www.glavis-hd.com/</t>
         </is>
       </c>
-      <c r="D4" s="39" t="inlineStr">
+      <c r="D4" s="40" t="inlineStr">
         <is>
           <t>HDサイトから</t>
         </is>
@@ -2722,7 +2764,7 @@
           <t>https://www.glavis-hd.com/company/message/</t>
         </is>
       </c>
-      <c r="D6" s="40" t="inlineStr">
+      <c r="D6" s="33" t="inlineStr">
         <is>
           <t>HDサイトから</t>
         </is>
@@ -2802,7 +2844,7 @@
           <t>https://www.glavis-hd.com/recruit/</t>
         </is>
       </c>
-      <c r="D8" s="40" t="inlineStr">
+      <c r="D8" s="33" t="inlineStr">
         <is>
           <t>HDサイトから</t>
         </is>
@@ -2962,7 +3004,7 @@
           <t>https://www.glavis-hd.com/site_policy/</t>
         </is>
       </c>
-      <c r="D12" s="40" t="inlineStr">
+      <c r="D12" s="33" t="inlineStr">
         <is>
           <t>HDサイトから</t>
         </is>
